--- a/lot_02.xlsx
+++ b/lot_02.xlsx
@@ -14,11 +14,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Services de proximite" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Artisanat &amp; BTP'!$A$3:$J$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Artisanat &amp; BTP'!$A$3:$J$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Beaute &amp; Bien-etre'!$A$3:$J$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Restauration'!$A$3:$J$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Automobile'!$A$3:$J$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Services de proximite'!$A$3:$J$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Services de proximite'!$A$3:$J$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -67,7 +67,7 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="0092400E"/>
+      <color rgb="00991B1B"/>
       <sz val="11"/>
     </font>
     <font>
@@ -89,13 +89,13 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00374151"/>
+      <color rgb="0092400E"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00991B1B"/>
+      <color rgb="00374151"/>
       <sz val="11"/>
     </font>
   </fonts>
@@ -113,7 +113,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FEF3C7"/>
+        <fgColor rgb="00FEE2E2"/>
       </patternFill>
     </fill>
     <fill>
@@ -123,12 +123,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F3F4F6"/>
+        <fgColor rgb="00FEF3C7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FEE2E2"/>
+        <fgColor rgb="00F3F4F6"/>
       </patternFill>
     </fill>
   </fills>
@@ -206,7 +206,13 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -214,12 +220,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -589,7 +589,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -607,7 +607,7 @@
     <row r="1" ht="34" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Artisanat &amp; BTP  ·  6 prospects</t>
+          <t>Artisanat &amp; BTP  ·  7 prospects</t>
         </is>
       </c>
     </row>
@@ -673,29 +673,29 @@
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>celo-gaz.com</t>
+          <t>lambert-licorni.fr</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>Celo gaz</t>
+          <t>Lambert Licorni</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>54</t>
         </is>
       </c>
       <c r="E4" s="8" t="n">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="F4" s="7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G4" s="9" t="inlineStr">
         <is>
@@ -714,93 +714,93 @@
       </c>
       <c r="J4" s="12" t="inlineStr">
         <is>
-          <t>non responsive | pas de @media | pas de flex/grid | pas de variables CSS | CSS tres court (434B) | aucun radius/ombre</t>
+          <t>balises &lt;font&gt; (16) | non responsive | pas de @media | pas de flex/grid | pas de variables CSS | CSS tres court (434B) | aucun radius/ombre</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="13" t="inlineStr">
         <is>
-          <t>atelier-delaunay.fr</t>
+          <t>celo-gaz.com</t>
         </is>
       </c>
       <c r="B5" s="14" t="inlineStr">
         <is>
-          <t>Atelier Delaunay</t>
+          <t>Celo gaz</t>
         </is>
       </c>
       <c r="C5" s="15" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="D5" s="16" t="inlineStr">
         <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="E5" s="8" t="n">
-        <v>41</v>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="E5" s="17" t="n">
+        <v>46</v>
       </c>
       <c r="F5" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="G5" s="17" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H5" s="17" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="I5" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J5" s="19" t="inlineStr">
-        <is>
-          <t>layout en tableaux (25) | bgcolor= | doctype ancien | non responsive | &lt;br&gt; en masse</t>
+        <v>3</v>
+      </c>
+      <c r="G5" s="18" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H5" s="19" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="I5" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J5" s="21" t="inlineStr">
+        <is>
+          <t>non responsive | pas de @media | pas de flex/grid | pas de variables CSS | CSS tres court (434B) | aucun radius/ombre</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>h4b.fr</t>
+          <t>atelier-delaunay.fr</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Henri De Quatres Barbes</t>
+          <t>Atelier Delaunay</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="n">
-        <v>39</v>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="E6" s="17" t="n">
+        <v>41</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
-      <c r="H6" s="10" t="inlineStr">
-        <is>
-          <t>oui</t>
+      <c r="H6" s="9" t="inlineStr">
+        <is>
+          <t>non</t>
         </is>
       </c>
       <c r="I6" s="11" t="inlineStr">
@@ -810,19 +810,19 @@
       </c>
       <c r="J6" s="12" t="inlineStr">
         <is>
-          <t>doctype ancien | non responsive | images .gif | pas de @media | pas de variables CSS</t>
+          <t>layout en tableaux (25) | bgcolor= | doctype ancien | non responsive | &lt;br&gt; en masse</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="13" t="inlineStr">
         <is>
-          <t>begrand.fr</t>
+          <t>h4b.fr</t>
         </is>
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>Entreprise Begrand</t>
+          <t>Henri De Quatres Barbes</t>
         </is>
       </c>
       <c r="C7" s="15" t="inlineStr">
@@ -835,68 +835,68 @@
           <t>75</t>
         </is>
       </c>
-      <c r="E7" s="20" t="n">
-        <v>33</v>
+      <c r="E7" s="17" t="n">
+        <v>39</v>
       </c>
       <c r="F7" s="16" t="n">
-        <v>6</v>
-      </c>
-      <c r="G7" s="17" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H7" s="21" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="G7" s="18" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H7" s="19" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="I7" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J7" s="19" t="inlineStr">
-        <is>
-          <t>balises &lt;font&gt; (3) | doctype ancien | non responsive | document.write</t>
+      <c r="I7" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J7" s="21" t="inlineStr">
+        <is>
+          <t>doctype ancien | non responsive | images .gif | pas de @media | pas de variables CSS</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>brunelli.fr</t>
+          <t>begrand.fr</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Brunelli</t>
+          <t>Entreprise Begrand</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="E8" s="20" t="n">
-        <v>29</v>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="E8" s="22" t="n">
+        <v>33</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G8" s="9" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
-      <c r="H8" s="9" t="inlineStr">
-        <is>
-          <t>non</t>
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t>oui</t>
         </is>
       </c>
       <c r="I8" s="11" t="inlineStr">
@@ -906,60 +906,108 @@
       </c>
       <c r="J8" s="12" t="inlineStr">
         <is>
-          <t>frameset | doctype ancien | non responsive</t>
+          <t>balises &lt;font&gt; (3) | doctype ancien | non responsive | document.write</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="13" t="inlineStr">
         <is>
+          <t>brunelli.fr</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>Brunelli</t>
+        </is>
+      </c>
+      <c r="C9" s="15" t="inlineStr">
+        <is>
+          <t>Nancy</t>
+        </is>
+      </c>
+      <c r="D9" s="16" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="n">
+        <v>29</v>
+      </c>
+      <c r="F9" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="G9" s="18" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H9" s="18" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I9" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J9" s="21" t="inlineStr">
+        <is>
+          <t>frameset | doctype ancien | non responsive</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
           <t>alazard-sas.com</t>
         </is>
       </c>
-      <c r="B9" s="14" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>Alazard</t>
         </is>
       </c>
-      <c r="C9" s="15" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>Paris</t>
         </is>
       </c>
-      <c r="D9" s="16" t="inlineStr">
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>75</t>
         </is>
       </c>
-      <c r="E9" s="20" t="n">
+      <c r="E10" s="22" t="n">
         <v>29</v>
       </c>
-      <c r="F9" s="16" t="n">
+      <c r="F10" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="G9" s="17" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H9" s="21" t="inlineStr">
+      <c r="G10" s="9" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H10" s="10" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="I9" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J9" s="19" t="inlineStr">
+      <c r="I10" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J10" s="12" t="inlineStr">
         <is>
           <t>non responsive | pas de @media</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:J9"/>
+  <autoFilter ref="A3:J10"/>
   <mergeCells count="2">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
@@ -971,6 +1019,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1084,7 +1133,7 @@
           <t>44</t>
         </is>
       </c>
-      <c r="E4" s="22" t="n">
+      <c r="E4" s="8" t="n">
         <v>56</v>
       </c>
       <c r="F4" s="7" t="n">
@@ -1132,28 +1181,28 @@
           <t>69</t>
         </is>
       </c>
-      <c r="E5" s="22" t="n">
+      <c r="E5" s="8" t="n">
         <v>56</v>
       </c>
       <c r="F5" s="16" t="n">
         <v>6</v>
       </c>
-      <c r="G5" s="17" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H5" s="21" t="inlineStr">
+      <c r="G5" s="18" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H5" s="19" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="I5" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J5" s="19" t="inlineStr">
+      <c r="I5" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J5" s="21" t="inlineStr">
         <is>
           <t>balises &lt;font&gt; (48) | non responsive | pas de @media | pas de flex/grid | pas de variables CSS | CSS tres court (434B) | aucun radius/ombre</t>
         </is>
@@ -1180,7 +1229,7 @@
           <t>75</t>
         </is>
       </c>
-      <c r="E6" s="22" t="n">
+      <c r="E6" s="8" t="n">
         <v>56</v>
       </c>
       <c r="F6" s="7" t="n">
@@ -1228,28 +1277,28 @@
           <t>69</t>
         </is>
       </c>
-      <c r="E7" s="8" t="n">
+      <c r="E7" s="17" t="n">
         <v>46</v>
       </c>
       <c r="F7" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="G7" s="17" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H7" s="21" t="inlineStr">
+      <c r="G7" s="18" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H7" s="19" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="I7" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J7" s="19" t="inlineStr">
+      <c r="I7" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J7" s="21" t="inlineStr">
         <is>
           <t>non responsive | pas de @media | pas de flex/grid | pas de variables CSS | CSS tres court (434B) | aucun radius/ombre</t>
         </is>
@@ -1276,7 +1325,7 @@
           <t>75</t>
         </is>
       </c>
-      <c r="E8" s="8" t="n">
+      <c r="E8" s="17" t="n">
         <v>46</v>
       </c>
       <c r="F8" s="7" t="n">
@@ -1324,28 +1373,28 @@
           <t>76</t>
         </is>
       </c>
-      <c r="E9" s="8" t="n">
+      <c r="E9" s="17" t="n">
         <v>42</v>
       </c>
       <c r="F9" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="G9" s="17" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H9" s="21" t="inlineStr">
+      <c r="G9" s="18" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H9" s="19" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="I9" s="18" t="inlineStr">
+      <c r="I9" s="20" t="inlineStr">
         <is>
           <t>webacappella 4.6.18 free (win)</t>
         </is>
       </c>
-      <c r="J9" s="19" t="inlineStr">
+      <c r="J9" s="21" t="inlineStr">
         <is>
           <t>doctype ancien | non responsive | document.write | pas de @media | pas de flex/grid</t>
         </is>
@@ -1372,7 +1421,7 @@
           <t>75</t>
         </is>
       </c>
-      <c r="E10" s="8" t="n">
+      <c r="E10" s="17" t="n">
         <v>41</v>
       </c>
       <c r="F10" s="7" t="n">
@@ -1526,7 +1575,7 @@
           <t>31</t>
         </is>
       </c>
-      <c r="E4" s="8" t="n">
+      <c r="E4" s="17" t="n">
         <v>42</v>
       </c>
       <c r="F4" s="7" t="n">
@@ -1574,28 +1623,28 @@
           <t>75</t>
         </is>
       </c>
-      <c r="E5" s="8" t="n">
+      <c r="E5" s="17" t="n">
         <v>39</v>
       </c>
       <c r="F5" s="16" t="n">
         <v>8</v>
       </c>
-      <c r="G5" s="17" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H5" s="17" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="I5" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J5" s="19" t="inlineStr">
+      <c r="G5" s="18" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H5" s="18" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I5" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J5" s="21" t="inlineStr">
         <is>
           <t>layout en tableaux (8) | bgcolor= | sans doctype | non responsive</t>
         </is>
@@ -1622,7 +1671,7 @@
           <t>31</t>
         </is>
       </c>
-      <c r="E6" s="8" t="n">
+      <c r="E6" s="17" t="n">
         <v>39</v>
       </c>
       <c r="F6" s="7" t="n">
@@ -1670,28 +1719,28 @@
           <t>31</t>
         </is>
       </c>
-      <c r="E7" s="8" t="n">
+      <c r="E7" s="17" t="n">
         <v>38</v>
       </c>
       <c r="F7" s="16" t="n">
         <v>8</v>
       </c>
-      <c r="G7" s="17" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H7" s="17" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="I7" s="18" t="inlineStr">
+      <c r="G7" s="18" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H7" s="18" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I7" s="20" t="inlineStr">
         <is>
           <t>wordpress 3.7.41</t>
         </is>
       </c>
-      <c r="J7" s="19" t="inlineStr">
+      <c r="J7" s="21" t="inlineStr">
         <is>
           <t>doctype ancien | non responsive | pas de @media | pas de flex/grid</t>
         </is>
@@ -1718,7 +1767,7 @@
           <t>69</t>
         </is>
       </c>
-      <c r="E8" s="8" t="n">
+      <c r="E8" s="17" t="n">
         <v>37</v>
       </c>
       <c r="F8" s="7" t="n">
@@ -1766,28 +1815,28 @@
           <t>75</t>
         </is>
       </c>
-      <c r="E9" s="8" t="n">
+      <c r="E9" s="17" t="n">
         <v>37</v>
       </c>
       <c r="F9" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="G9" s="17" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H9" s="17" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="I9" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J9" s="19" t="inlineStr">
+      <c r="G9" s="18" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H9" s="18" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I9" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J9" s="21" t="inlineStr">
         <is>
           <t>non responsive | document.write | pas de @media | police vintage</t>
         </is>
@@ -1814,7 +1863,7 @@
           <t>59</t>
         </is>
       </c>
-      <c r="E10" s="8" t="n">
+      <c r="E10" s="17" t="n">
         <v>37</v>
       </c>
       <c r="F10" s="7" t="n">
@@ -1968,7 +2017,7 @@
           <t>49</t>
         </is>
       </c>
-      <c r="E4" s="8" t="n">
+      <c r="E4" s="17" t="n">
         <v>46</v>
       </c>
       <c r="F4" s="7" t="n">
@@ -2016,28 +2065,28 @@
           <t>69</t>
         </is>
       </c>
-      <c r="E5" s="8" t="n">
+      <c r="E5" s="17" t="n">
         <v>44</v>
       </c>
       <c r="F5" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="G5" s="17" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H5" s="17" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="I5" s="18" t="inlineStr">
+      <c r="G5" s="18" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H5" s="18" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I5" s="20" t="inlineStr">
         <is>
           <t>spip 3.1.3 [23214] - sarka-spip 3.4.6 [99617]</t>
         </is>
       </c>
-      <c r="J5" s="19" t="inlineStr">
+      <c r="J5" s="21" t="inlineStr">
         <is>
           <t>non responsive | images .gif | document.write | pas de @media | pas de flex/grid | aucun radius/ombre</t>
         </is>
@@ -2064,7 +2113,7 @@
           <t>35</t>
         </is>
       </c>
-      <c r="E6" s="8" t="n">
+      <c r="E6" s="17" t="n">
         <v>41</v>
       </c>
       <c r="F6" s="7" t="n">
@@ -2112,28 +2161,28 @@
           <t>57</t>
         </is>
       </c>
-      <c r="E7" s="8" t="n">
+      <c r="E7" s="17" t="n">
         <v>41</v>
       </c>
       <c r="F7" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="G7" s="17" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H7" s="21" t="inlineStr">
+      <c r="G7" s="18" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H7" s="19" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="I7" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J7" s="19" t="inlineStr">
+      <c r="I7" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J7" s="21" t="inlineStr">
         <is>
           <t>non responsive | pas de @media | pas de flex/grid | pas de variables CSS | police vintage</t>
         </is>
@@ -2160,7 +2209,7 @@
           <t>44</t>
         </is>
       </c>
-      <c r="E8" s="20" t="n">
+      <c r="E8" s="22" t="n">
         <v>32</v>
       </c>
       <c r="F8" s="7" t="n">
@@ -2208,28 +2257,28 @@
           <t>25</t>
         </is>
       </c>
-      <c r="E9" s="20" t="n">
+      <c r="E9" s="22" t="n">
         <v>29</v>
       </c>
       <c r="F9" s="16" t="n">
         <v>8</v>
       </c>
-      <c r="G9" s="17" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H9" s="17" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="I9" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J9" s="19" t="inlineStr">
+      <c r="G9" s="18" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H9" s="18" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I9" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J9" s="21" t="inlineStr">
         <is>
           <t>frameset | doctype ancien | non responsive</t>
         </is>
@@ -2256,7 +2305,7 @@
           <t>30</t>
         </is>
       </c>
-      <c r="E10" s="20" t="n">
+      <c r="E10" s="22" t="n">
         <v>25</v>
       </c>
       <c r="F10" s="7" t="n">
@@ -2308,7 +2357,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2326,7 +2375,7 @@
     <row r="1" ht="34" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Services de proximite  ·  5 prospects</t>
+          <t>Services de proximite  ·  7 prospects</t>
         </is>
       </c>
     </row>
@@ -2392,12 +2441,12 @@
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>pressingleluxembourg.com</t>
+          <t>depuy.free.fr</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>Le Luxembourg</t>
+          <t>SAV Depuy</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
@@ -2410,11 +2459,11 @@
           <t>75</t>
         </is>
       </c>
-      <c r="E4" s="20" t="n">
-        <v>32</v>
+      <c r="E4" s="17" t="n">
+        <v>38</v>
       </c>
       <c r="F4" s="7" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G4" s="9" t="inlineStr">
         <is>
@@ -2433,93 +2482,93 @@
       </c>
       <c r="J4" s="12" t="inlineStr">
         <is>
-          <t>non responsive | pas de @media | pas de variables CSS</t>
+          <t>balises &lt;font&gt; (57) | bgcolor= | sans doctype | non responsive | images .gif</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="13" t="inlineStr">
         <is>
-          <t>autourducycle.fr</t>
+          <t>cs2m.fr</t>
         </is>
       </c>
       <c r="B5" s="14" t="inlineStr">
         <is>
-          <t>Autour du Cycle</t>
+          <t>CS2M - Cordonnerie Serrurerie</t>
         </is>
       </c>
       <c r="C5" s="15" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="D5" s="16" t="inlineStr">
         <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="E5" s="20" t="n">
-        <v>29</v>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="E5" s="22" t="n">
+        <v>34</v>
       </c>
       <c r="F5" s="16" t="n">
-        <v>6</v>
-      </c>
-      <c r="G5" s="17" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H5" s="21" t="inlineStr">
+        <v>5</v>
+      </c>
+      <c r="G5" s="18" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H5" s="19" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="I5" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J5" s="19" t="inlineStr">
-        <is>
-          <t>balises &lt;font&gt; (11) | non responsive | police vintage</t>
+      <c r="I5" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J5" s="21" t="inlineStr">
+        <is>
+          <t>non responsive | pas de @media | pas de flex/grid</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>alizes-pressing.fr</t>
+          <t>pressingleluxembourg.com</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Alizée Naturellement Pressing</t>
+          <t>Le Luxembourg</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="E6" s="20" t="n">
-        <v>28</v>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="E6" s="22" t="n">
+        <v>32</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="10" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H6" s="10" t="inlineStr">
-        <is>
-          <t>oui</t>
+        <v>5</v>
+      </c>
+      <c r="G6" s="9" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H6" s="9" t="inlineStr">
+        <is>
+          <t>non</t>
         </is>
       </c>
       <c r="I6" s="11" t="inlineStr">
@@ -2529,19 +2578,19 @@
       </c>
       <c r="J6" s="12" t="inlineStr">
         <is>
-          <t>pas de @media | pas de flex/grid | CSS tres court (506B) | aucun radius/ombre</t>
+          <t>non responsive | pas de @media | pas de variables CSS</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="13" t="inlineStr">
         <is>
-          <t>cycle-naturel.com</t>
+          <t>autourducycle.fr</t>
         </is>
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>Cycle Naturel</t>
+          <t>Autour du Cycle</t>
         </is>
       </c>
       <c r="C7" s="15" t="inlineStr">
@@ -2554,83 +2603,179 @@
           <t>75</t>
         </is>
       </c>
-      <c r="E7" s="20" t="n">
-        <v>25</v>
+      <c r="E7" s="22" t="n">
+        <v>29</v>
       </c>
       <c r="F7" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="G7" s="17" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H7" s="17" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="I7" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J7" s="19" t="inlineStr">
-        <is>
-          <t>frameset | non responsive</t>
+        <v>6</v>
+      </c>
+      <c r="G7" s="18" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H7" s="19" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="I7" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J7" s="21" t="inlineStr">
+        <is>
+          <t>balises &lt;font&gt; (11) | non responsive | police vintage</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
+          <t>alizes-pressing.fr</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Alizée Naturellement Pressing</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Lille</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="E8" s="22" t="n">
+        <v>28</v>
+      </c>
+      <c r="F8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="10" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="I8" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J8" s="12" t="inlineStr">
+        <is>
+          <t>pas de @media | pas de flex/grid | CSS tres court (506B) | aucun radius/ombre</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>cycle-naturel.com</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>Cycle Naturel</t>
+        </is>
+      </c>
+      <c r="C9" s="15" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="D9" s="16" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="n">
+        <v>25</v>
+      </c>
+      <c r="F9" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="G9" s="18" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H9" s="18" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I9" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J9" s="21" t="inlineStr">
+        <is>
+          <t>frameset | non responsive</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
           <t>3dinfomac.com</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>3D Informatique</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>Paris</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>75</t>
         </is>
       </c>
-      <c r="E8" s="20" t="n">
+      <c r="E10" s="22" t="n">
         <v>25</v>
       </c>
-      <c r="F8" s="7" t="n">
+      <c r="F10" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="G8" s="9" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H8" s="10" t="inlineStr">
+      <c r="G10" s="9" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H10" s="10" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="I8" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J8" s="12" t="inlineStr">
+      <c r="I10" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J10" s="12" t="inlineStr">
         <is>
           <t>balises &lt;font&gt; (7) | non responsive</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:J8"/>
+  <autoFilter ref="A3:J10"/>
   <mergeCells count="2">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
@@ -2641,6 +2786,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/lot_02.xlsx
+++ b/lot_02.xlsx
@@ -14,11 +14,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Services de proximite" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Artisanat &amp; BTP'!$A$3:$J$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Beaute &amp; Bien-etre'!$A$3:$J$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Restauration'!$A$3:$J$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Automobile'!$A$3:$J$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Services de proximite'!$A$3:$J$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Artisanat &amp; BTP'!$A$3:$K$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Beaute &amp; Bien-etre'!$A$3:$K$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Restauration'!$A$3:$K$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Automobile'!$A$3:$K$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Services de proximite'!$A$3:$K$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -27,7 +27,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -95,6 +95,12 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
+      <color rgb="00111827"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
       <color rgb="00374151"/>
       <sz val="11"/>
     </font>
@@ -158,7 +164,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -172,6 +178,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -200,6 +209,9 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -221,8 +233,14 @@
     <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -589,19 +607,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="5" max="5"/>
     <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="62" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="62" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -614,7 +633,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Classés du site le plus indéfendable au moins pire. « Laideur » = score de design daté ; « Ancien. » = signaux d'abandon.</t>
+          <t>Classés du site le plus indéfendable au moins pire. « Laideur » = score de design daté ; « Ancien. » = signaux d'abandon. « Zone » est le centre de recherche, pas l'adresse : la commune réelle n'est indiquée que lorsque le site l'affiche.</t>
         </is>
       </c>
     </row>
@@ -631,40 +650,45 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Ville</t>
+          <t>Zone de recherche</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
+          <t>Commune réelle</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
           <t>Dép.</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>Laideur</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>Ancien.</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>Responsive</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>HTTPS</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>Techno</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>Ce qui cloche</t>
         </is>
@@ -686,81 +710,83 @@
           <t>Nancy</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D4" s="7" t="inlineStr"/>
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>54</t>
         </is>
       </c>
-      <c r="E4" s="8" t="n">
+      <c r="F4" s="9" t="n">
         <v>56</v>
       </c>
-      <c r="F4" s="7" t="n">
+      <c r="G4" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="G4" s="9" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
       <c r="H4" s="10" t="inlineStr">
         <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I4" s="11" t="inlineStr">
+        <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="I4" s="11" t="inlineStr">
+      <c r="J4" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J4" s="12" t="inlineStr">
+      <c r="K4" s="13" t="inlineStr">
         <is>
           <t>balises &lt;font&gt; (16) | non responsive | pas de @media | pas de flex/grid | pas de variables CSS | CSS tres court (434B) | aucun radius/ombre</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>celo-gaz.com</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr">
+      <c r="B5" s="15" t="inlineStr">
         <is>
           <t>Celo gaz</t>
         </is>
       </c>
-      <c r="C5" s="15" t="inlineStr">
+      <c r="C5" s="16" t="inlineStr">
         <is>
           <t>Paris</t>
         </is>
       </c>
-      <c r="D5" s="16" t="inlineStr">
+      <c r="D5" s="17" t="inlineStr"/>
+      <c r="E5" s="18" t="inlineStr">
         <is>
           <t>75</t>
         </is>
       </c>
-      <c r="E5" s="17" t="n">
+      <c r="F5" s="19" t="n">
         <v>46</v>
       </c>
-      <c r="F5" s="16" t="n">
+      <c r="G5" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="G5" s="18" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H5" s="19" t="inlineStr">
+      <c r="H5" s="20" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I5" s="21" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="I5" s="20" t="inlineStr">
+      <c r="J5" s="22" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J5" s="21" t="inlineStr">
+      <c r="K5" s="23" t="inlineStr">
         <is>
           <t>non responsive | pas de @media | pas de flex/grid | pas de variables CSS | CSS tres court (434B) | aucun radius/ombre</t>
         </is>
@@ -782,81 +808,87 @@
           <t>Le Havre</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr"/>
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>76</t>
         </is>
       </c>
-      <c r="E6" s="17" t="n">
+      <c r="F6" s="19" t="n">
         <v>41</v>
       </c>
-      <c r="F6" s="7" t="n">
+      <c r="G6" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="G6" s="9" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H6" s="9" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="I6" s="11" t="inlineStr">
+      <c r="H6" s="10" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="J6" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J6" s="12" t="inlineStr">
+      <c r="K6" s="13" t="inlineStr">
         <is>
           <t>layout en tableaux (25) | bgcolor= | doctype ancien | non responsive | &lt;br&gt; en masse</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>h4b.fr</t>
         </is>
       </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B7" s="15" t="inlineStr">
         <is>
           <t>Henri De Quatres Barbes</t>
         </is>
       </c>
-      <c r="C7" s="15" t="inlineStr">
+      <c r="C7" s="16" t="inlineStr">
         <is>
           <t>Paris</t>
         </is>
       </c>
-      <c r="D7" s="16" t="inlineStr">
+      <c r="D7" s="24" t="inlineStr">
+        <is>
+          <t>Boulogne Billancourt (92100)</t>
+        </is>
+      </c>
+      <c r="E7" s="18" t="inlineStr">
         <is>
           <t>75</t>
         </is>
       </c>
-      <c r="E7" s="17" t="n">
+      <c r="F7" s="19" t="n">
         <v>39</v>
       </c>
-      <c r="F7" s="16" t="n">
+      <c r="G7" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="G7" s="18" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H7" s="19" t="inlineStr">
+      <c r="H7" s="20" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I7" s="21" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="I7" s="20" t="inlineStr">
+      <c r="J7" s="22" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J7" s="21" t="inlineStr">
+      <c r="K7" s="23" t="inlineStr">
         <is>
           <t>doctype ancien | non responsive | images .gif | pas de @media | pas de variables CSS</t>
         </is>
@@ -878,81 +910,83 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D8" s="7" t="inlineStr"/>
+      <c r="E8" s="8" t="inlineStr">
         <is>
           <t>75</t>
         </is>
       </c>
-      <c r="E8" s="22" t="n">
+      <c r="F8" s="25" t="n">
         <v>33</v>
       </c>
-      <c r="F8" s="7" t="n">
+      <c r="G8" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="G8" s="9" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
       <c r="H8" s="10" t="inlineStr">
         <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I8" s="11" t="inlineStr">
+        <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="I8" s="11" t="inlineStr">
+      <c r="J8" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J8" s="12" t="inlineStr">
+      <c r="K8" s="13" t="inlineStr">
         <is>
           <t>balises &lt;font&gt; (3) | doctype ancien | non responsive | document.write</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>brunelli.fr</t>
         </is>
       </c>
-      <c r="B9" s="14" t="inlineStr">
+      <c r="B9" s="15" t="inlineStr">
         <is>
           <t>Brunelli</t>
         </is>
       </c>
-      <c r="C9" s="15" t="inlineStr">
+      <c r="C9" s="16" t="inlineStr">
         <is>
           <t>Nancy</t>
         </is>
       </c>
-      <c r="D9" s="16" t="inlineStr">
+      <c r="D9" s="17" t="inlineStr"/>
+      <c r="E9" s="18" t="inlineStr">
         <is>
           <t>54</t>
         </is>
       </c>
-      <c r="E9" s="22" t="n">
+      <c r="F9" s="25" t="n">
         <v>29</v>
       </c>
-      <c r="F9" s="16" t="n">
+      <c r="G9" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="G9" s="18" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H9" s="18" t="inlineStr">
+      <c r="H9" s="20" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
       <c r="I9" s="20" t="inlineStr">
         <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="J9" s="22" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J9" s="21" t="inlineStr">
+      <c r="K9" s="23" t="inlineStr">
         <is>
           <t>frameset | doctype ancien | non responsive</t>
         </is>
@@ -974,43 +1008,48 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="D10" s="26" t="inlineStr">
+        <is>
+          <t>LENTREPRISE (94500)</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
         <is>
           <t>75</t>
         </is>
       </c>
-      <c r="E10" s="22" t="n">
+      <c r="F10" s="25" t="n">
         <v>29</v>
       </c>
-      <c r="F10" s="7" t="n">
+      <c r="G10" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="G10" s="9" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
       <c r="H10" s="10" t="inlineStr">
         <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I10" s="11" t="inlineStr">
+        <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="I10" s="11" t="inlineStr">
+      <c r="J10" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J10" s="12" t="inlineStr">
+      <c r="K10" s="13" t="inlineStr">
         <is>
           <t>non responsive | pas de @media</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:J10"/>
+  <autoFilter ref="A3:K10"/>
   <mergeCells count="2">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A1:K1"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId1"/>
@@ -1031,19 +1070,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="5" max="5"/>
     <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="62" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="62" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -1056,7 +1096,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Classés du site le plus indéfendable au moins pire. « Laideur » = score de design daté ; « Ancien. » = signaux d'abandon.</t>
+          <t>Classés du site le plus indéfendable au moins pire. « Laideur » = score de design daté ; « Ancien. » = signaux d'abandon. « Zone » est le centre de recherche, pas l'adresse : la commune réelle n'est indiquée que lorsque le site l'affiche.</t>
         </is>
       </c>
     </row>
@@ -1073,40 +1113,45 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Ville</t>
+          <t>Zone de recherche</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
+          <t>Commune réelle</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
           <t>Dép.</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>Laideur</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>Ancien.</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>Responsive</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>HTTPS</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>Techno</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>Ce qui cloche</t>
         </is>
@@ -1128,81 +1173,83 @@
           <t>Nantes</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D4" s="7" t="inlineStr"/>
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>44</t>
         </is>
       </c>
-      <c r="E4" s="8" t="n">
+      <c r="F4" s="9" t="n">
         <v>56</v>
       </c>
-      <c r="F4" s="7" t="n">
+      <c r="G4" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="G4" s="9" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
       <c r="H4" s="10" t="inlineStr">
         <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I4" s="11" t="inlineStr">
+        <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="I4" s="11" t="inlineStr">
+      <c r="J4" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J4" s="12" t="inlineStr">
+      <c r="K4" s="13" t="inlineStr">
         <is>
           <t>balises &lt;font&gt; (19) | non responsive | pas de @media | pas de flex/grid | pas de variables CSS | CSS tres court (434B) | aucun radius/ombre</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>bc-coiffure-oullins.fr</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr">
+      <c r="B5" s="15" t="inlineStr">
         <is>
           <t>BC Coiffure</t>
         </is>
       </c>
-      <c r="C5" s="15" t="inlineStr">
+      <c r="C5" s="16" t="inlineStr">
         <is>
           <t>Lyon</t>
         </is>
       </c>
-      <c r="D5" s="16" t="inlineStr">
+      <c r="D5" s="17" t="inlineStr"/>
+      <c r="E5" s="18" t="inlineStr">
         <is>
           <t>69</t>
         </is>
       </c>
-      <c r="E5" s="8" t="n">
+      <c r="F5" s="9" t="n">
         <v>56</v>
       </c>
-      <c r="F5" s="16" t="n">
+      <c r="G5" s="18" t="n">
         <v>6</v>
       </c>
-      <c r="G5" s="18" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H5" s="19" t="inlineStr">
+      <c r="H5" s="20" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I5" s="21" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="I5" s="20" t="inlineStr">
+      <c r="J5" s="22" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J5" s="21" t="inlineStr">
+      <c r="K5" s="23" t="inlineStr">
         <is>
           <t>balises &lt;font&gt; (48) | non responsive | pas de @media | pas de flex/grid | pas de variables CSS | CSS tres court (434B) | aucun radius/ombre</t>
         </is>
@@ -1224,81 +1271,83 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr"/>
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>75</t>
         </is>
       </c>
-      <c r="E6" s="8" t="n">
+      <c r="F6" s="9" t="n">
         <v>56</v>
       </c>
-      <c r="F6" s="7" t="n">
+      <c r="G6" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="G6" s="9" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
       <c r="H6" s="10" t="inlineStr">
         <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I6" s="11" t="inlineStr">
+        <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="I6" s="11" t="inlineStr">
+      <c r="J6" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J6" s="12" t="inlineStr">
+      <c r="K6" s="13" t="inlineStr">
         <is>
           <t>balises &lt;font&gt; (2) | non responsive | pas de @media | pas de flex/grid | pas de variables CSS | CSS tres court (434B) | aucun radius/ombre</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>amazen-spa.fr</t>
         </is>
       </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B7" s="15" t="inlineStr">
         <is>
           <t>Amazen</t>
         </is>
       </c>
-      <c r="C7" s="15" t="inlineStr">
+      <c r="C7" s="16" t="inlineStr">
         <is>
           <t>Lyon</t>
         </is>
       </c>
-      <c r="D7" s="16" t="inlineStr">
+      <c r="D7" s="17" t="inlineStr"/>
+      <c r="E7" s="18" t="inlineStr">
         <is>
           <t>69</t>
         </is>
       </c>
-      <c r="E7" s="17" t="n">
+      <c r="F7" s="19" t="n">
         <v>46</v>
       </c>
-      <c r="F7" s="16" t="n">
+      <c r="G7" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="G7" s="18" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H7" s="19" t="inlineStr">
+      <c r="H7" s="20" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I7" s="21" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="I7" s="20" t="inlineStr">
+      <c r="J7" s="22" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J7" s="21" t="inlineStr">
+      <c r="K7" s="23" t="inlineStr">
         <is>
           <t>non responsive | pas de @media | pas de flex/grid | pas de variables CSS | CSS tres court (434B) | aucun radius/ombre</t>
         </is>
@@ -1320,81 +1369,83 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D8" s="7" t="inlineStr"/>
+      <c r="E8" s="8" t="inlineStr">
         <is>
           <t>75</t>
         </is>
       </c>
-      <c r="E8" s="17" t="n">
+      <c r="F8" s="19" t="n">
         <v>46</v>
       </c>
-      <c r="F8" s="7" t="n">
+      <c r="G8" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="G8" s="9" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
       <c r="H8" s="10" t="inlineStr">
         <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I8" s="11" t="inlineStr">
+        <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="I8" s="11" t="inlineStr">
+      <c r="J8" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J8" s="12" t="inlineStr">
+      <c r="K8" s="13" t="inlineStr">
         <is>
           <t>non responsive | pas de @media | pas de flex/grid | pas de variables CSS | CSS tres court (434B) | aucun radius/ombre</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>lavillasaintmarc.com</t>
         </is>
       </c>
-      <c r="B9" s="14" t="inlineStr">
+      <c r="B9" s="15" t="inlineStr">
         <is>
           <t>La Villa Saint-Marc</t>
         </is>
       </c>
-      <c r="C9" s="15" t="inlineStr">
+      <c r="C9" s="16" t="inlineStr">
         <is>
           <t>Rouen</t>
         </is>
       </c>
-      <c r="D9" s="16" t="inlineStr">
+      <c r="D9" s="17" t="inlineStr"/>
+      <c r="E9" s="18" t="inlineStr">
         <is>
           <t>76</t>
         </is>
       </c>
-      <c r="E9" s="17" t="n">
+      <c r="F9" s="19" t="n">
         <v>42</v>
       </c>
-      <c r="F9" s="16" t="n">
+      <c r="G9" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="G9" s="18" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H9" s="19" t="inlineStr">
+      <c r="H9" s="20" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I9" s="21" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="I9" s="20" t="inlineStr">
+      <c r="J9" s="22" t="inlineStr">
         <is>
           <t>webacappella 4.6.18 free (win)</t>
         </is>
       </c>
-      <c r="J9" s="21" t="inlineStr">
+      <c r="K9" s="23" t="inlineStr">
         <is>
           <t>doctype ancien | non responsive | document.write | pas de @media | pas de flex/grid</t>
         </is>
@@ -1416,43 +1467,44 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="D10" s="7" t="inlineStr"/>
+      <c r="E10" s="8" t="inlineStr">
         <is>
           <t>75</t>
         </is>
       </c>
-      <c r="E10" s="17" t="n">
+      <c r="F10" s="19" t="n">
         <v>41</v>
       </c>
-      <c r="F10" s="7" t="n">
+      <c r="G10" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="G10" s="9" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H10" s="9" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="I10" s="11" t="inlineStr">
+      <c r="H10" s="10" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I10" s="10" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="J10" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J10" s="12" t="inlineStr">
+      <c r="K10" s="13" t="inlineStr">
         <is>
           <t>non responsive | pas de @media | px uniquement | pas de variables CSS | aucun radius/ombre</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:J10"/>
+  <autoFilter ref="A3:K10"/>
   <mergeCells count="2">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A1:K1"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId1"/>
@@ -1473,19 +1525,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="5" max="5"/>
     <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="62" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="62" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -1498,7 +1551,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Classés du site le plus indéfendable au moins pire. « Laideur » = score de design daté ; « Ancien. » = signaux d'abandon.</t>
+          <t>Classés du site le plus indéfendable au moins pire. « Laideur » = score de design daté ; « Ancien. » = signaux d'abandon. « Zone » est le centre de recherche, pas l'adresse : la commune réelle n'est indiquée que lorsque le site l'affiche.</t>
         </is>
       </c>
     </row>
@@ -1515,40 +1568,45 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Ville</t>
+          <t>Zone de recherche</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
+          <t>Commune réelle</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
           <t>Dép.</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>Laideur</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>Ancien.</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>Responsive</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>HTTPS</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>Techno</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>Ce qui cloche</t>
         </is>
@@ -1570,81 +1628,83 @@
           <t>Toulouse</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D4" s="7" t="inlineStr"/>
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="E4" s="17" t="n">
+      <c r="F4" s="19" t="n">
         <v>42</v>
       </c>
-      <c r="F4" s="7" t="n">
+      <c r="G4" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="G4" s="9" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
       <c r="H4" s="10" t="inlineStr">
         <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I4" s="11" t="inlineStr">
+        <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="I4" s="11" t="inlineStr">
+      <c r="J4" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J4" s="12" t="inlineStr">
+      <c r="K4" s="13" t="inlineStr">
         <is>
           <t>&lt;center&gt; | non responsive | pas de @media | pas de flex/grid | pas de variables CSS</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>surlepouce.libanais.free.fr</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr">
+      <c r="B5" s="15" t="inlineStr">
         <is>
           <t>Sur le Pouce</t>
         </is>
       </c>
-      <c r="C5" s="15" t="inlineStr">
+      <c r="C5" s="16" t="inlineStr">
         <is>
           <t>Paris</t>
         </is>
       </c>
-      <c r="D5" s="16" t="inlineStr">
+      <c r="D5" s="17" t="inlineStr"/>
+      <c r="E5" s="18" t="inlineStr">
         <is>
           <t>75</t>
         </is>
       </c>
-      <c r="E5" s="17" t="n">
+      <c r="F5" s="19" t="n">
         <v>39</v>
       </c>
-      <c r="F5" s="16" t="n">
+      <c r="G5" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="G5" s="18" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H5" s="18" t="inlineStr">
+      <c r="H5" s="20" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
       <c r="I5" s="20" t="inlineStr">
         <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="J5" s="22" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J5" s="21" t="inlineStr">
+      <c r="K5" s="23" t="inlineStr">
         <is>
           <t>layout en tableaux (8) | bgcolor= | sans doctype | non responsive</t>
         </is>
@@ -1666,81 +1726,83 @@
           <t>Toulouse</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr"/>
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="E6" s="17" t="n">
+      <c r="F6" s="19" t="n">
         <v>39</v>
       </c>
-      <c r="F6" s="7" t="n">
+      <c r="G6" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="G6" s="9" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
       <c r="H6" s="10" t="inlineStr">
         <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I6" s="11" t="inlineStr">
+        <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="I6" s="11" t="inlineStr">
+      <c r="J6" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J6" s="12" t="inlineStr">
+      <c r="K6" s="13" t="inlineStr">
         <is>
           <t>layout en tableaux (4) | bgcolor= | sans doctype | non responsive</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>toulousefruitsdemer.fr</t>
         </is>
       </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B7" s="15" t="inlineStr">
         <is>
           <t>La Cabane</t>
         </is>
       </c>
-      <c r="C7" s="15" t="inlineStr">
+      <c r="C7" s="16" t="inlineStr">
         <is>
           <t>Toulouse</t>
         </is>
       </c>
-      <c r="D7" s="16" t="inlineStr">
+      <c r="D7" s="17" t="inlineStr"/>
+      <c r="E7" s="18" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="E7" s="17" t="n">
+      <c r="F7" s="19" t="n">
         <v>38</v>
       </c>
-      <c r="F7" s="16" t="n">
+      <c r="G7" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="G7" s="18" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H7" s="18" t="inlineStr">
+      <c r="H7" s="20" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
       <c r="I7" s="20" t="inlineStr">
         <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="J7" s="22" t="inlineStr">
+        <is>
           <t>wordpress 3.7.41</t>
         </is>
       </c>
-      <c r="J7" s="21" t="inlineStr">
+      <c r="K7" s="23" t="inlineStr">
         <is>
           <t>doctype ancien | non responsive | pas de @media | pas de flex/grid</t>
         </is>
@@ -1762,81 +1824,87 @@
           <t>Lyon</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D8" s="7" t="inlineStr"/>
+      <c r="E8" s="8" t="inlineStr">
         <is>
           <t>69</t>
         </is>
       </c>
-      <c r="E8" s="17" t="n">
+      <c r="F8" s="19" t="n">
         <v>37</v>
       </c>
-      <c r="F8" s="7" t="n">
+      <c r="G8" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="G8" s="9" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
       <c r="H8" s="10" t="inlineStr">
         <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I8" s="11" t="inlineStr">
+        <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="I8" s="11" t="inlineStr">
+      <c r="J8" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J8" s="12" t="inlineStr">
+      <c r="K8" s="13" t="inlineStr">
         <is>
           <t>layout en tableaux (95) | &lt;center&gt; | non responsive | &lt;br&gt; en masse</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>bistrobest.fr</t>
         </is>
       </c>
-      <c r="B9" s="14" t="inlineStr">
+      <c r="B9" s="15" t="inlineStr">
         <is>
           <t>Bistro Best</t>
         </is>
       </c>
-      <c r="C9" s="15" t="inlineStr">
+      <c r="C9" s="16" t="inlineStr">
         <is>
           <t>Paris</t>
         </is>
       </c>
-      <c r="D9" s="16" t="inlineStr">
+      <c r="D9" s="24" t="inlineStr">
+        <is>
+          <t>Marly (78160)</t>
+        </is>
+      </c>
+      <c r="E9" s="18" t="inlineStr">
         <is>
           <t>75</t>
         </is>
       </c>
-      <c r="E9" s="17" t="n">
+      <c r="F9" s="19" t="n">
         <v>37</v>
       </c>
-      <c r="F9" s="16" t="n">
+      <c r="G9" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="G9" s="18" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H9" s="18" t="inlineStr">
+      <c r="H9" s="20" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
       <c r="I9" s="20" t="inlineStr">
         <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="J9" s="22" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J9" s="21" t="inlineStr">
+      <c r="K9" s="23" t="inlineStr">
         <is>
           <t>non responsive | document.write | pas de @media | police vintage</t>
         </is>
@@ -1858,43 +1926,44 @@
           <t>Lille</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="D10" s="7" t="inlineStr"/>
+      <c r="E10" s="8" t="inlineStr">
         <is>
           <t>59</t>
         </is>
       </c>
-      <c r="E10" s="17" t="n">
+      <c r="F10" s="19" t="n">
         <v>37</v>
       </c>
-      <c r="F10" s="7" t="n">
+      <c r="G10" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="G10" s="9" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
       <c r="H10" s="10" t="inlineStr">
         <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I10" s="11" t="inlineStr">
+        <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="I10" s="11" t="inlineStr">
+      <c r="J10" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J10" s="12" t="inlineStr">
+      <c r="K10" s="13" t="inlineStr">
         <is>
           <t>non responsive | pas de @media | pas de flex/grid | aucun radius/ombre</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:J10"/>
+  <autoFilter ref="A3:K10"/>
   <mergeCells count="2">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A1:K1"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId1"/>
@@ -1915,19 +1984,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="5" max="5"/>
     <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="62" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="62" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -1940,7 +2010,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Classés du site le plus indéfendable au moins pire. « Laideur » = score de design daté ; « Ancien. » = signaux d'abandon.</t>
+          <t>Classés du site le plus indéfendable au moins pire. « Laideur » = score de design daté ; « Ancien. » = signaux d'abandon. « Zone » est le centre de recherche, pas l'adresse : la commune réelle n'est indiquée que lorsque le site l'affiche.</t>
         </is>
       </c>
     </row>
@@ -1957,40 +2027,45 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Ville</t>
+          <t>Zone de recherche</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
+          <t>Commune réelle</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
           <t>Dép.</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>Laideur</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>Ancien.</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>Responsive</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>HTTPS</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>Techno</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>Ce qui cloche</t>
         </is>
@@ -1999,94 +2074,96 @@
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>batteries-energie.com</t>
+          <t>garage-massot-aussonne.fr</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>Atlantic Batteries</t>
+          <t>Garage Massot</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Angers</t>
-        </is>
-      </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="E4" s="17" t="n">
-        <v>46</v>
-      </c>
-      <c r="F4" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="G4" s="9" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
+          <t>Toulouse</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr"/>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="n">
+        <v>56</v>
+      </c>
+      <c r="G4" s="8" t="n">
+        <v>6</v>
       </c>
       <c r="H4" s="10" t="inlineStr">
         <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I4" s="11" t="inlineStr">
+        <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="I4" s="11" t="inlineStr">
+      <c r="J4" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J4" s="12" t="inlineStr">
-        <is>
-          <t>non responsive | pas de @media | pas de flex/grid | pas de variables CSS | CSS tres court (434B) | aucun radius/ombre</t>
+      <c r="K4" s="13" t="inlineStr">
+        <is>
+          <t>balises &lt;font&gt; (4) | non responsive | pas de @media | pas de flex/grid | pas de variables CSS | CSS tres court (434B) | aucun radius/ombre</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>attelage-remorque-lyon.com</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr">
+      <c r="B5" s="15" t="inlineStr">
         <is>
           <t>Attelage et remorque de Lyon</t>
         </is>
       </c>
-      <c r="C5" s="15" t="inlineStr">
+      <c r="C5" s="16" t="inlineStr">
         <is>
           <t>Lyon</t>
         </is>
       </c>
-      <c r="D5" s="16" t="inlineStr">
+      <c r="D5" s="17" t="inlineStr"/>
+      <c r="E5" s="18" t="inlineStr">
         <is>
           <t>69</t>
         </is>
       </c>
-      <c r="E5" s="17" t="n">
+      <c r="F5" s="19" t="n">
         <v>44</v>
       </c>
-      <c r="F5" s="16" t="n">
+      <c r="G5" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="G5" s="18" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H5" s="18" t="inlineStr">
+      <c r="H5" s="20" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
       <c r="I5" s="20" t="inlineStr">
         <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="J5" s="22" t="inlineStr">
+        <is>
           <t>spip 3.1.3 [23214] - sarka-spip 3.4.6 [99617]</t>
         </is>
       </c>
-      <c r="J5" s="21" t="inlineStr">
+      <c r="K5" s="23" t="inlineStr">
         <is>
           <t>non responsive | images .gif | document.write | pas de @media | pas de flex/grid | aucun radius/ombre</t>
         </is>
@@ -2108,81 +2185,87 @@
           <t>Rennes</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr"/>
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="E6" s="17" t="n">
+      <c r="F6" s="19" t="n">
         <v>41</v>
       </c>
-      <c r="F6" s="7" t="n">
+      <c r="G6" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="G6" s="9" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
       <c r="H6" s="10" t="inlineStr">
         <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I6" s="11" t="inlineStr">
+        <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="I6" s="11" t="inlineStr">
+      <c r="J6" s="12" t="inlineStr">
         <is>
           <t>website builder 12.0.7</t>
         </is>
       </c>
-      <c r="J6" s="12" t="inlineStr">
+      <c r="K6" s="13" t="inlineStr">
         <is>
           <t>doctype ancien | non responsive | pas de @media | pas de flex/grid | pas de variables CSS</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>aap57.fr</t>
         </is>
       </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B7" s="15" t="inlineStr">
         <is>
           <t>Accueil Auto Pièces 57</t>
         </is>
       </c>
-      <c r="C7" s="15" t="inlineStr">
+      <c r="C7" s="16" t="inlineStr">
         <is>
           <t>Metz</t>
         </is>
       </c>
-      <c r="D7" s="16" t="inlineStr">
+      <c r="D7" s="24" t="inlineStr">
+        <is>
+          <t>THAON (88150)</t>
+        </is>
+      </c>
+      <c r="E7" s="18" t="inlineStr">
         <is>
           <t>57</t>
         </is>
       </c>
-      <c r="E7" s="17" t="n">
+      <c r="F7" s="19" t="n">
         <v>41</v>
       </c>
-      <c r="F7" s="16" t="n">
+      <c r="G7" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="G7" s="18" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H7" s="19" t="inlineStr">
+      <c r="H7" s="20" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I7" s="21" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="I7" s="20" t="inlineStr">
+      <c r="J7" s="22" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J7" s="21" t="inlineStr">
+      <c r="K7" s="23" t="inlineStr">
         <is>
           <t>non responsive | pas de @media | pas de flex/grid | pas de variables CSS | police vintage</t>
         </is>
@@ -2204,81 +2287,83 @@
           <t>Nantes</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D8" s="7" t="inlineStr"/>
+      <c r="E8" s="8" t="inlineStr">
         <is>
           <t>44</t>
         </is>
       </c>
-      <c r="E8" s="22" t="n">
+      <c r="F8" s="25" t="n">
         <v>32</v>
       </c>
-      <c r="F8" s="7" t="n">
+      <c r="G8" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="G8" s="9" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
       <c r="H8" s="10" t="inlineStr">
         <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I8" s="11" t="inlineStr">
+        <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="I8" s="11" t="inlineStr">
+      <c r="J8" s="12" t="inlineStr">
         <is>
           <t>wp rocket 3.23.1</t>
         </is>
       </c>
-      <c r="J8" s="12" t="inlineStr">
+      <c r="K8" s="13" t="inlineStr">
         <is>
           <t>non responsive | pas de @media | pas de variables CSS</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>saone-auto.fr</t>
         </is>
       </c>
-      <c r="B9" s="14" t="inlineStr">
+      <c r="B9" s="15" t="inlineStr">
         <is>
           <t>Garage Renault</t>
         </is>
       </c>
-      <c r="C9" s="15" t="inlineStr">
+      <c r="C9" s="16" t="inlineStr">
         <is>
           <t>Besancon</t>
         </is>
       </c>
-      <c r="D9" s="16" t="inlineStr">
+      <c r="D9" s="17" t="inlineStr"/>
+      <c r="E9" s="18" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E9" s="22" t="n">
+      <c r="F9" s="25" t="n">
         <v>29</v>
       </c>
-      <c r="F9" s="16" t="n">
+      <c r="G9" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="G9" s="18" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H9" s="18" t="inlineStr">
+      <c r="H9" s="20" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
       <c r="I9" s="20" t="inlineStr">
         <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="J9" s="22" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J9" s="21" t="inlineStr">
+      <c r="K9" s="23" t="inlineStr">
         <is>
           <t>frameset | doctype ancien | non responsive</t>
         </is>
@@ -2300,43 +2385,44 @@
           <t>Nimes</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="D10" s="7" t="inlineStr"/>
+      <c r="E10" s="8" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E10" s="22" t="n">
+      <c r="F10" s="25" t="n">
         <v>25</v>
       </c>
-      <c r="F10" s="7" t="n">
+      <c r="G10" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="G10" s="9" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H10" s="9" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="I10" s="11" t="inlineStr">
+      <c r="H10" s="10" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I10" s="10" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="J10" s="12" t="inlineStr">
         <is>
           <t>ort - ovh redirect technology</t>
         </is>
       </c>
-      <c r="J10" s="12" t="inlineStr">
+      <c r="K10" s="13" t="inlineStr">
         <is>
           <t>frameset | non responsive</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:J10"/>
+  <autoFilter ref="A3:K10"/>
   <mergeCells count="2">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A1:K1"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId1"/>
@@ -2357,19 +2443,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="5" max="5"/>
     <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="62" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="62" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -2382,7 +2469,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Classés du site le plus indéfendable au moins pire. « Laideur » = score de design daté ; « Ancien. » = signaux d'abandon.</t>
+          <t>Classés du site le plus indéfendable au moins pire. « Laideur » = score de design daté ; « Ancien. » = signaux d'abandon. « Zone » est le centre de recherche, pas l'adresse : la commune réelle n'est indiquée que lorsque le site l'affiche.</t>
         </is>
       </c>
     </row>
@@ -2399,40 +2486,45 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Ville</t>
+          <t>Zone de recherche</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
+          <t>Commune réelle</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
           <t>Dép.</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>Laideur</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>Ancien.</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>Responsive</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>HTTPS</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>Techno</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>Ce qui cloche</t>
         </is>
@@ -2454,81 +2546,87 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D4" s="26" t="inlineStr">
+        <is>
+          <t>Saint Brice sous Fort (95350)</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>75</t>
         </is>
       </c>
-      <c r="E4" s="17" t="n">
+      <c r="F4" s="19" t="n">
         <v>38</v>
       </c>
-      <c r="F4" s="7" t="n">
+      <c r="G4" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="G4" s="9" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H4" s="9" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="I4" s="11" t="inlineStr">
+      <c r="H4" s="10" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I4" s="10" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="J4" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J4" s="12" t="inlineStr">
+      <c r="K4" s="13" t="inlineStr">
         <is>
           <t>balises &lt;font&gt; (57) | bgcolor= | sans doctype | non responsive | images .gif</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>cs2m.fr</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr">
+      <c r="B5" s="15" t="inlineStr">
         <is>
           <t>CS2M - Cordonnerie Serrurerie</t>
         </is>
       </c>
-      <c r="C5" s="15" t="inlineStr">
+      <c r="C5" s="16" t="inlineStr">
         <is>
           <t>Toulouse</t>
         </is>
       </c>
-      <c r="D5" s="16" t="inlineStr">
+      <c r="D5" s="17" t="inlineStr"/>
+      <c r="E5" s="18" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="E5" s="22" t="n">
+      <c r="F5" s="25" t="n">
         <v>34</v>
       </c>
-      <c r="F5" s="16" t="n">
+      <c r="G5" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="G5" s="18" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H5" s="19" t="inlineStr">
+      <c r="H5" s="20" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I5" s="21" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="I5" s="20" t="inlineStr">
+      <c r="J5" s="22" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J5" s="21" t="inlineStr">
+      <c r="K5" s="23" t="inlineStr">
         <is>
           <t>non responsive | pas de @media | pas de flex/grid</t>
         </is>
@@ -2550,177 +2648,185 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr"/>
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>75</t>
         </is>
       </c>
-      <c r="E6" s="22" t="n">
+      <c r="F6" s="25" t="n">
         <v>32</v>
       </c>
-      <c r="F6" s="7" t="n">
+      <c r="G6" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="G6" s="9" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H6" s="9" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="I6" s="11" t="inlineStr">
+      <c r="H6" s="10" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="J6" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J6" s="12" t="inlineStr">
+      <c r="K6" s="13" t="inlineStr">
         <is>
           <t>non responsive | pas de @media | pas de variables CSS</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="13" t="inlineStr">
-        <is>
-          <t>autourducycle.fr</t>
-        </is>
-      </c>
-      <c r="B7" s="14" t="inlineStr">
-        <is>
-          <t>Autour du Cycle</t>
-        </is>
-      </c>
-      <c r="C7" s="15" t="inlineStr">
-        <is>
-          <t>Paris</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="E7" s="22" t="n">
-        <v>29</v>
-      </c>
-      <c r="F7" s="16" t="n">
-        <v>6</v>
-      </c>
-      <c r="G7" s="18" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H7" s="19" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>floriansbikes.com</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="inlineStr">
+        <is>
+          <t>Florian's Bikes</t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>Toulouse</t>
+        </is>
+      </c>
+      <c r="D7" s="17" t="inlineStr"/>
+      <c r="E7" s="18" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="F7" s="25" t="n">
+        <v>32</v>
+      </c>
+      <c r="G7" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="H7" s="20" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I7" s="21" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="I7" s="20" t="inlineStr">
+      <c r="J7" s="22" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J7" s="21" t="inlineStr">
-        <is>
-          <t>balises &lt;font&gt; (11) | non responsive | police vintage</t>
+      <c r="K7" s="23" t="inlineStr">
+        <is>
+          <t>non responsive | pas de @media | pas de variables CSS</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>alizes-pressing.fr</t>
+          <t>autourducycle.fr</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Alizée Naturellement Pressing</t>
+          <t>Autour du Cycle</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Lille</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="E8" s="22" t="n">
-        <v>28</v>
-      </c>
-      <c r="F8" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="10" t="inlineStr">
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="D8" s="26" t="inlineStr">
+        <is>
+          <t>La Varenne Saint Hilaire (94210)</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="F8" s="25" t="n">
+        <v>29</v>
+      </c>
+      <c r="G8" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I8" s="11" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="H8" s="10" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="I8" s="11" t="inlineStr">
+      <c r="J8" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J8" s="12" t="inlineStr">
-        <is>
-          <t>pas de @media | pas de flex/grid | CSS tres court (506B) | aucun radius/ombre</t>
+      <c r="K8" s="13" t="inlineStr">
+        <is>
+          <t>balises &lt;font&gt; (11) | non responsive | police vintage</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>cycle-naturel.com</t>
         </is>
       </c>
-      <c r="B9" s="14" t="inlineStr">
+      <c r="B9" s="15" t="inlineStr">
         <is>
           <t>Cycle Naturel</t>
         </is>
       </c>
-      <c r="C9" s="15" t="inlineStr">
+      <c r="C9" s="16" t="inlineStr">
         <is>
           <t>Paris</t>
         </is>
       </c>
-      <c r="D9" s="16" t="inlineStr">
+      <c r="D9" s="17" t="inlineStr"/>
+      <c r="E9" s="18" t="inlineStr">
         <is>
           <t>75</t>
         </is>
       </c>
-      <c r="E9" s="22" t="n">
+      <c r="F9" s="25" t="n">
         <v>25</v>
       </c>
-      <c r="F9" s="16" t="n">
+      <c r="G9" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="G9" s="18" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H9" s="18" t="inlineStr">
+      <c r="H9" s="20" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
       <c r="I9" s="20" t="inlineStr">
         <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="J9" s="22" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J9" s="21" t="inlineStr">
+      <c r="K9" s="23" t="inlineStr">
         <is>
           <t>frameset | non responsive</t>
         </is>
@@ -2742,43 +2848,44 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="D10" s="7" t="inlineStr"/>
+      <c r="E10" s="8" t="inlineStr">
         <is>
           <t>75</t>
         </is>
       </c>
-      <c r="E10" s="22" t="n">
+      <c r="F10" s="25" t="n">
         <v>25</v>
       </c>
-      <c r="F10" s="7" t="n">
+      <c r="G10" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="G10" s="9" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
       <c r="H10" s="10" t="inlineStr">
         <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I10" s="11" t="inlineStr">
+        <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="I10" s="11" t="inlineStr">
+      <c r="J10" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J10" s="12" t="inlineStr">
+      <c r="K10" s="13" t="inlineStr">
         <is>
           <t>balises &lt;font&gt; (7) | non responsive</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:J10"/>
+  <autoFilter ref="A3:K10"/>
   <mergeCells count="2">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A1:K1"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId1"/>

--- a/lot_02.xlsx
+++ b/lot_02.xlsx
@@ -89,14 +89,14 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="0092400E"/>
-      <sz val="11"/>
+      <color rgb="00111827"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00111827"/>
-      <sz val="10"/>
+      <color rgb="0092400E"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -182,7 +182,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -212,13 +212,10 @@
     <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -233,14 +230,17 @@
     <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -697,23 +697,27 @@
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>lambert-licorni.fr</t>
+          <t>atlantiquegouttieres.fr</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>Lambert Licorni</t>
+          <t>Atlantique Gouttières</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Nancy</t>
-        </is>
-      </c>
-      <c r="D4" s="7" t="inlineStr"/>
+          <t>La Rochelle</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>Aytré (17440)</t>
+        </is>
+      </c>
       <c r="E4" s="8" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>17</t>
         </is>
       </c>
       <c r="F4" s="9" t="n">
@@ -739,95 +743,99 @@
       </c>
       <c r="K4" s="13" t="inlineStr">
         <is>
-          <t>balises &lt;font&gt; (16) | non responsive | pas de @media | pas de flex/grid | pas de variables CSS | CSS tres court (434B) | aucun radius/ombre</t>
+          <t>balises &lt;font&gt; (20) | non responsive | pas de @media | pas de flex/grid | pas de variables CSS | CSS tres court (434B) | aucun radius/ombre</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="14" t="inlineStr">
         <is>
-          <t>celo-gaz.com</t>
+          <t>doussot.fr</t>
         </is>
       </c>
       <c r="B5" s="15" t="inlineStr">
         <is>
-          <t>Celo gaz</t>
+          <t>Doussot Service Énergie</t>
         </is>
       </c>
       <c r="C5" s="16" t="inlineStr">
         <is>
-          <t>Paris</t>
-        </is>
-      </c>
-      <c r="D5" s="17" t="inlineStr"/>
+          <t>Dijon</t>
+        </is>
+      </c>
+      <c r="D5" s="17" t="inlineStr">
+        <is>
+          <t>Dijon (21000)</t>
+        </is>
+      </c>
       <c r="E5" s="18" t="inlineStr">
         <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="F5" s="19" t="n">
-        <v>46</v>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="n">
+        <v>56</v>
       </c>
       <c r="G5" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="H5" s="20" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="I5" s="21" t="inlineStr">
+        <v>6</v>
+      </c>
+      <c r="H5" s="19" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I5" s="20" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="J5" s="22" t="inlineStr">
+      <c r="J5" s="21" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K5" s="23" t="inlineStr">
-        <is>
-          <t>non responsive | pas de @media | pas de flex/grid | pas de variables CSS | CSS tres court (434B) | aucun radius/ombre</t>
+      <c r="K5" s="22" t="inlineStr">
+        <is>
+          <t>balises &lt;font&gt; (4) | non responsive | pas de @media | pas de flex/grid | pas de variables CSS | CSS tres court (434B) | aucun radius/ombre</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>atelier-delaunay.fr</t>
+          <t>lambert-licorni.fr</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Atelier Delaunay</t>
+          <t>Lambert Licorni</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Le Havre</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr"/>
+          <t>Nancy</t>
+        </is>
+      </c>
+      <c r="D6" s="23" t="inlineStr"/>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="F6" s="19" t="n">
-        <v>41</v>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="n">
+        <v>56</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H6" s="10" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
-      <c r="I6" s="10" t="inlineStr">
-        <is>
-          <t>non</t>
+      <c r="I6" s="11" t="inlineStr">
+        <is>
+          <t>oui</t>
         </is>
       </c>
       <c r="J6" s="12" t="inlineStr">
@@ -837,19 +845,19 @@
       </c>
       <c r="K6" s="13" t="inlineStr">
         <is>
-          <t>layout en tableaux (25) | bgcolor= | doctype ancien | non responsive | &lt;br&gt; en masse</t>
+          <t>balises &lt;font&gt; (16) | non responsive | pas de @media | pas de flex/grid | pas de variables CSS | CSS tres court (434B) | aucun radius/ombre</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>h4b.fr</t>
+          <t>celo-gaz.com</t>
         </is>
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>Henri De Quatres Barbes</t>
+          <t>Celo gaz</t>
         </is>
       </c>
       <c r="C7" s="16" t="inlineStr">
@@ -857,79 +865,75 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="D7" s="24" t="inlineStr">
-        <is>
-          <t>Boulogne Billancourt (92100)</t>
-        </is>
-      </c>
+      <c r="D7" s="24" t="inlineStr"/>
       <c r="E7" s="18" t="inlineStr">
         <is>
           <t>75</t>
         </is>
       </c>
-      <c r="F7" s="19" t="n">
-        <v>39</v>
+      <c r="F7" s="25" t="n">
+        <v>46</v>
       </c>
       <c r="G7" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="H7" s="20" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="I7" s="21" t="inlineStr">
+      <c r="H7" s="19" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I7" s="20" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="J7" s="22" t="inlineStr">
+      <c r="J7" s="21" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K7" s="23" t="inlineStr">
-        <is>
-          <t>doctype ancien | non responsive | images .gif | pas de @media | pas de variables CSS</t>
+      <c r="K7" s="22" t="inlineStr">
+        <is>
+          <t>non responsive | pas de @media | pas de flex/grid | pas de variables CSS | CSS tres court (434B) | aucun radius/ombre</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>begrand.fr</t>
+          <t>atelier-delaunay.fr</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Entreprise Begrand</t>
+          <t>Atelier Delaunay</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Paris</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr"/>
+          <t>Le Havre</t>
+        </is>
+      </c>
+      <c r="D8" s="23" t="inlineStr"/>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>76</t>
         </is>
       </c>
       <c r="F8" s="25" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H8" s="10" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
-      <c r="I8" s="11" t="inlineStr">
-        <is>
-          <t>oui</t>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>non</t>
         </is>
       </c>
       <c r="J8" s="12" t="inlineStr">
@@ -939,99 +943,95 @@
       </c>
       <c r="K8" s="13" t="inlineStr">
         <is>
-          <t>balises &lt;font&gt; (3) | doctype ancien | non responsive | document.write</t>
+          <t>layout en tableaux (25) | bgcolor= | doctype ancien | non responsive | &lt;br&gt; en masse</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>brunelli.fr</t>
+          <t>begrand.fr</t>
         </is>
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>Brunelli</t>
+          <t>Entreprise Begrand</t>
         </is>
       </c>
       <c r="C9" s="16" t="inlineStr">
         <is>
-          <t>Nancy</t>
-        </is>
-      </c>
-      <c r="D9" s="17" t="inlineStr"/>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="D9" s="24" t="inlineStr"/>
       <c r="E9" s="18" t="inlineStr">
         <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="F9" s="25" t="n">
-        <v>29</v>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="F9" s="26" t="n">
+        <v>33</v>
       </c>
       <c r="G9" s="18" t="n">
-        <v>8</v>
-      </c>
-      <c r="H9" s="20" t="inlineStr">
+        <v>6</v>
+      </c>
+      <c r="H9" s="19" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
       <c r="I9" s="20" t="inlineStr">
         <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="J9" s="22" t="inlineStr">
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J9" s="21" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K9" s="23" t="inlineStr">
-        <is>
-          <t>frameset | doctype ancien | non responsive</t>
+      <c r="K9" s="22" t="inlineStr">
+        <is>
+          <t>balises &lt;font&gt; (3) | doctype ancien | non responsive | document.write</t>
         </is>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>alazard-sas.com</t>
+          <t>brunelli.fr</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Alazard</t>
+          <t>Brunelli</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Paris</t>
-        </is>
-      </c>
-      <c r="D10" s="26" t="inlineStr">
-        <is>
-          <t>LENTREPRISE (94500)</t>
-        </is>
-      </c>
+          <t>Nancy</t>
+        </is>
+      </c>
+      <c r="D10" s="23" t="inlineStr"/>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="F10" s="25" t="n">
+          <t>54</t>
+        </is>
+      </c>
+      <c r="F10" s="26" t="n">
         <v>29</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H10" s="10" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
-      <c r="I10" s="11" t="inlineStr">
-        <is>
-          <t>oui</t>
+      <c r="I10" s="10" t="inlineStr">
+        <is>
+          <t>non</t>
         </is>
       </c>
       <c r="J10" s="12" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="K10" s="13" t="inlineStr">
         <is>
-          <t>non responsive | pas de @media</t>
+          <t>frameset | doctype ancien | non responsive</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
           <t>Nantes</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr"/>
+      <c r="D4" s="23" t="inlineStr"/>
       <c r="E4" s="8" t="inlineStr">
         <is>
           <t>44</t>
@@ -1222,7 +1222,7 @@
           <t>Lyon</t>
         </is>
       </c>
-      <c r="D5" s="17" t="inlineStr"/>
+      <c r="D5" s="24" t="inlineStr"/>
       <c r="E5" s="18" t="inlineStr">
         <is>
           <t>69</t>
@@ -1234,22 +1234,22 @@
       <c r="G5" s="18" t="n">
         <v>6</v>
       </c>
-      <c r="H5" s="20" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="I5" s="21" t="inlineStr">
+      <c r="H5" s="19" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I5" s="20" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="J5" s="22" t="inlineStr">
+      <c r="J5" s="21" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K5" s="23" t="inlineStr">
+      <c r="K5" s="22" t="inlineStr">
         <is>
           <t>balises &lt;font&gt; (48) | non responsive | pas de @media | pas de flex/grid | pas de variables CSS | CSS tres court (434B) | aucun radius/ombre</t>
         </is>
@@ -1271,7 +1271,7 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr"/>
+      <c r="D6" s="23" t="inlineStr"/>
       <c r="E6" s="8" t="inlineStr">
         <is>
           <t>75</t>
@@ -1320,34 +1320,34 @@
           <t>Lyon</t>
         </is>
       </c>
-      <c r="D7" s="17" t="inlineStr"/>
+      <c r="D7" s="24" t="inlineStr"/>
       <c r="E7" s="18" t="inlineStr">
         <is>
           <t>69</t>
         </is>
       </c>
-      <c r="F7" s="19" t="n">
+      <c r="F7" s="25" t="n">
         <v>46</v>
       </c>
       <c r="G7" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="H7" s="20" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="I7" s="21" t="inlineStr">
+      <c r="H7" s="19" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I7" s="20" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="J7" s="22" t="inlineStr">
+      <c r="J7" s="21" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K7" s="23" t="inlineStr">
+      <c r="K7" s="22" t="inlineStr">
         <is>
           <t>non responsive | pas de @media | pas de flex/grid | pas de variables CSS | CSS tres court (434B) | aucun radius/ombre</t>
         </is>
@@ -1369,13 +1369,13 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr"/>
+      <c r="D8" s="23" t="inlineStr"/>
       <c r="E8" s="8" t="inlineStr">
         <is>
           <t>75</t>
         </is>
       </c>
-      <c r="F8" s="19" t="n">
+      <c r="F8" s="25" t="n">
         <v>46</v>
       </c>
       <c r="G8" s="8" t="n">
@@ -1418,34 +1418,34 @@
           <t>Rouen</t>
         </is>
       </c>
-      <c r="D9" s="17" t="inlineStr"/>
+      <c r="D9" s="24" t="inlineStr"/>
       <c r="E9" s="18" t="inlineStr">
         <is>
           <t>76</t>
         </is>
       </c>
-      <c r="F9" s="19" t="n">
+      <c r="F9" s="25" t="n">
         <v>42</v>
       </c>
       <c r="G9" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="H9" s="20" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="I9" s="21" t="inlineStr">
+      <c r="H9" s="19" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I9" s="20" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="J9" s="22" t="inlineStr">
+      <c r="J9" s="21" t="inlineStr">
         <is>
           <t>webacappella 4.6.18 free (win)</t>
         </is>
       </c>
-      <c r="K9" s="23" t="inlineStr">
+      <c r="K9" s="22" t="inlineStr">
         <is>
           <t>doctype ancien | non responsive | document.write | pas de @media | pas de flex/grid</t>
         </is>
@@ -1467,13 +1467,13 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr"/>
+      <c r="D10" s="23" t="inlineStr"/>
       <c r="E10" s="8" t="inlineStr">
         <is>
           <t>75</t>
         </is>
       </c>
-      <c r="F10" s="19" t="n">
+      <c r="F10" s="25" t="n">
         <v>41</v>
       </c>
       <c r="G10" s="8" t="n">
@@ -1615,27 +1615,31 @@
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>bouilloncapitole.fr</t>
+          <t>friteriedumynck.fr</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>Le Bouillon Capitole</t>
+          <t>Friterie du Mynck</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Toulouse</t>
-        </is>
-      </c>
-      <c r="D4" s="7" t="inlineStr"/>
+          <t>Dunkerque</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>Dunkerque (59140)</t>
+        </is>
+      </c>
       <c r="E4" s="8" t="inlineStr">
         <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="F4" s="19" t="n">
-        <v>42</v>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="n">
+        <v>56</v>
       </c>
       <c r="G4" s="8" t="n">
         <v>6</v>
@@ -1657,95 +1661,95 @@
       </c>
       <c r="K4" s="13" t="inlineStr">
         <is>
-          <t>&lt;center&gt; | non responsive | pas de @media | pas de flex/grid | pas de variables CSS</t>
+          <t>balises &lt;font&gt; (1) | non responsive | pas de @media | pas de flex/grid | pas de variables CSS | CSS tres court (434B) | aucun radius/ombre</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="14" t="inlineStr">
         <is>
-          <t>surlepouce.libanais.free.fr</t>
+          <t>bouilloncapitole.fr</t>
         </is>
       </c>
       <c r="B5" s="15" t="inlineStr">
         <is>
-          <t>Sur le Pouce</t>
+          <t>Le Bouillon Capitole</t>
         </is>
       </c>
       <c r="C5" s="16" t="inlineStr">
         <is>
-          <t>Paris</t>
-        </is>
-      </c>
-      <c r="D5" s="17" t="inlineStr"/>
+          <t>Toulouse</t>
+        </is>
+      </c>
+      <c r="D5" s="24" t="inlineStr"/>
       <c r="E5" s="18" t="inlineStr">
         <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="F5" s="19" t="n">
-        <v>39</v>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="F5" s="25" t="n">
+        <v>42</v>
       </c>
       <c r="G5" s="18" t="n">
-        <v>8</v>
-      </c>
-      <c r="H5" s="20" t="inlineStr">
+        <v>6</v>
+      </c>
+      <c r="H5" s="19" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
       <c r="I5" s="20" t="inlineStr">
         <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="J5" s="22" t="inlineStr">
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J5" s="21" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K5" s="23" t="inlineStr">
-        <is>
-          <t>layout en tableaux (8) | bgcolor= | sans doctype | non responsive</t>
+      <c r="K5" s="22" t="inlineStr">
+        <is>
+          <t>&lt;center&gt; | non responsive | pas de @media | pas de flex/grid | pas de variables CSS</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>gindalle.fr</t>
+          <t>surlepouce.libanais.free.fr</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Gin Dalle</t>
+          <t>Sur le Pouce</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Toulouse</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr"/>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="D6" s="23" t="inlineStr"/>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="F6" s="19" t="n">
+          <t>75</t>
+        </is>
+      </c>
+      <c r="F6" s="25" t="n">
         <v>39</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H6" s="10" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
-      <c r="I6" s="11" t="inlineStr">
-        <is>
-          <t>oui</t>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>non</t>
         </is>
       </c>
       <c r="J6" s="12" t="inlineStr">
@@ -1755,19 +1759,19 @@
       </c>
       <c r="K6" s="13" t="inlineStr">
         <is>
-          <t>layout en tableaux (4) | bgcolor= | sans doctype | non responsive</t>
+          <t>layout en tableaux (8) | bgcolor= | sans doctype | non responsive</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>toulousefruitsdemer.fr</t>
+          <t>gindalle.fr</t>
         </is>
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>La Cabane</t>
+          <t>Gin Dalle</t>
         </is>
       </c>
       <c r="C7" s="16" t="inlineStr">
@@ -1775,138 +1779,134 @@
           <t>Toulouse</t>
         </is>
       </c>
-      <c r="D7" s="17" t="inlineStr"/>
+      <c r="D7" s="24" t="inlineStr"/>
       <c r="E7" s="18" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="F7" s="19" t="n">
-        <v>38</v>
+      <c r="F7" s="25" t="n">
+        <v>39</v>
       </c>
       <c r="G7" s="18" t="n">
-        <v>8</v>
-      </c>
-      <c r="H7" s="20" t="inlineStr">
+        <v>6</v>
+      </c>
+      <c r="H7" s="19" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
       <c r="I7" s="20" t="inlineStr">
         <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="J7" s="22" t="inlineStr">
-        <is>
-          <t>wordpress 3.7.41</t>
-        </is>
-      </c>
-      <c r="K7" s="23" t="inlineStr">
-        <is>
-          <t>doctype ancien | non responsive | pas de @media | pas de flex/grid</t>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J7" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K7" s="22" t="inlineStr">
+        <is>
+          <t>layout en tableaux (4) | bgcolor= | sans doctype | non responsive</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>crocknpizz.fr</t>
+          <t>toulousefruitsdemer.fr</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>C'rock n'pizz</t>
+          <t>La Cabane</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Lyon</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr"/>
+          <t>Toulouse</t>
+        </is>
+      </c>
+      <c r="D8" s="23" t="inlineStr"/>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="F8" s="19" t="n">
-        <v>37</v>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="F8" s="25" t="n">
+        <v>38</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H8" s="10" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
-      <c r="I8" s="11" t="inlineStr">
-        <is>
-          <t>oui</t>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>non</t>
         </is>
       </c>
       <c r="J8" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>wordpress 3.7.41</t>
         </is>
       </c>
       <c r="K8" s="13" t="inlineStr">
         <is>
-          <t>layout en tableaux (95) | &lt;center&gt; | non responsive | &lt;br&gt; en masse</t>
+          <t>doctype ancien | non responsive | pas de @media | pas de flex/grid</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>bistrobest.fr</t>
+          <t>crocknpizz.fr</t>
         </is>
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>Bistro Best</t>
+          <t>C'rock n'pizz</t>
         </is>
       </c>
       <c r="C9" s="16" t="inlineStr">
         <is>
-          <t>Paris</t>
-        </is>
-      </c>
-      <c r="D9" s="24" t="inlineStr">
-        <is>
-          <t>Marly (78160)</t>
-        </is>
-      </c>
+          <t>Lyon</t>
+        </is>
+      </c>
+      <c r="D9" s="24" t="inlineStr"/>
       <c r="E9" s="18" t="inlineStr">
         <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="F9" s="19" t="n">
+          <t>69</t>
+        </is>
+      </c>
+      <c r="F9" s="25" t="n">
         <v>37</v>
       </c>
       <c r="G9" s="18" t="n">
-        <v>5</v>
-      </c>
-      <c r="H9" s="20" t="inlineStr">
+        <v>6</v>
+      </c>
+      <c r="H9" s="19" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
       <c r="I9" s="20" t="inlineStr">
         <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="J9" s="22" t="inlineStr">
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J9" s="21" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K9" s="23" t="inlineStr">
-        <is>
-          <t>non responsive | document.write | pas de @media | police vintage</t>
+      <c r="K9" s="22" t="inlineStr">
+        <is>
+          <t>layout en tableaux (95) | &lt;center&gt; | non responsive | &lt;br&gt; en masse</t>
         </is>
       </c>
     </row>
@@ -1926,13 +1926,13 @@
           <t>Lille</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr"/>
+      <c r="D10" s="23" t="inlineStr"/>
       <c r="E10" s="8" t="inlineStr">
         <is>
           <t>59</t>
         </is>
       </c>
-      <c r="F10" s="19" t="n">
+      <c r="F10" s="25" t="n">
         <v>37</v>
       </c>
       <c r="G10" s="8" t="n">
@@ -2074,27 +2074,31 @@
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>garage-massot-aussonne.fr</t>
+          <t>toyotagarageclaudy.com</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>Garage Massot</t>
+          <t>Garage Claudy</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Toulouse</t>
-        </is>
-      </c>
-      <c r="D4" s="7" t="inlineStr"/>
+          <t>Lyon</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>Villeurbanne (69100)</t>
+        </is>
+      </c>
       <c r="E4" s="8" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>69</t>
         </is>
       </c>
       <c r="F4" s="9" t="n">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="G4" s="8" t="n">
         <v>6</v>
@@ -2116,83 +2120,83 @@
       </c>
       <c r="K4" s="13" t="inlineStr">
         <is>
-          <t>balises &lt;font&gt; (4) | non responsive | pas de @media | pas de flex/grid | pas de variables CSS | CSS tres court (434B) | aucun radius/ombre</t>
+          <t>balises &lt;font&gt; (2) | bgcolor= | doctype ancien | non responsive | images .gif | document.write | pas de @media | pas de flex/grid | pas de variables CSS | aucun radius/ombre</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="14" t="inlineStr">
         <is>
-          <t>attelage-remorque-lyon.com</t>
+          <t>garage-massot-aussonne.fr</t>
         </is>
       </c>
       <c r="B5" s="15" t="inlineStr">
         <is>
-          <t>Attelage et remorque de Lyon</t>
+          <t>Garage Massot</t>
         </is>
       </c>
       <c r="C5" s="16" t="inlineStr">
         <is>
-          <t>Lyon</t>
-        </is>
-      </c>
-      <c r="D5" s="17" t="inlineStr"/>
+          <t>Toulouse</t>
+        </is>
+      </c>
+      <c r="D5" s="24" t="inlineStr"/>
       <c r="E5" s="18" t="inlineStr">
         <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="F5" s="19" t="n">
-        <v>44</v>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="n">
+        <v>56</v>
       </c>
       <c r="G5" s="18" t="n">
-        <v>5</v>
-      </c>
-      <c r="H5" s="20" t="inlineStr">
+        <v>6</v>
+      </c>
+      <c r="H5" s="19" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
       <c r="I5" s="20" t="inlineStr">
         <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="J5" s="22" t="inlineStr">
-        <is>
-          <t>spip 3.1.3 [23214] - sarka-spip 3.4.6 [99617]</t>
-        </is>
-      </c>
-      <c r="K5" s="23" t="inlineStr">
-        <is>
-          <t>non responsive | images .gif | document.write | pas de @media | pas de flex/grid | aucun radius/ombre</t>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J5" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K5" s="22" t="inlineStr">
+        <is>
+          <t>balises &lt;font&gt; (4) | non responsive | pas de @media | pas de flex/grid | pas de variables CSS | CSS tres court (434B) | aucun radius/ombre</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>monsieur-embrayage-35.com</t>
+          <t>attelage-remorque-lyon.com</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Monsieur Embrayage</t>
+          <t>Attelage et remorque de Lyon</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Rennes</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr"/>
+          <t>Lyon</t>
+        </is>
+      </c>
+      <c r="D6" s="23" t="inlineStr"/>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="F6" s="19" t="n">
-        <v>41</v>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="F6" s="25" t="n">
+        <v>44</v>
       </c>
       <c r="G6" s="8" t="n">
         <v>5</v>
@@ -2202,72 +2206,68 @@
           <t>non</t>
         </is>
       </c>
-      <c r="I6" s="11" t="inlineStr">
-        <is>
-          <t>oui</t>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>non</t>
         </is>
       </c>
       <c r="J6" s="12" t="inlineStr">
         <is>
-          <t>website builder 12.0.7</t>
+          <t>spip 3.1.3 [23214] - sarka-spip 3.4.6 [99617]</t>
         </is>
       </c>
       <c r="K6" s="13" t="inlineStr">
         <is>
-          <t>doctype ancien | non responsive | pas de @media | pas de flex/grid | pas de variables CSS</t>
+          <t>non responsive | images .gif | document.write | pas de @media | pas de flex/grid | aucun radius/ombre</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>aap57.fr</t>
+          <t>monsieur-embrayage-35.com</t>
         </is>
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>Accueil Auto Pièces 57</t>
+          <t>Monsieur Embrayage</t>
         </is>
       </c>
       <c r="C7" s="16" t="inlineStr">
         <is>
-          <t>Metz</t>
-        </is>
-      </c>
-      <c r="D7" s="24" t="inlineStr">
-        <is>
-          <t>THAON (88150)</t>
-        </is>
-      </c>
+          <t>Rennes</t>
+        </is>
+      </c>
+      <c r="D7" s="24" t="inlineStr"/>
       <c r="E7" s="18" t="inlineStr">
         <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="F7" s="19" t="n">
+          <t>35</t>
+        </is>
+      </c>
+      <c r="F7" s="25" t="n">
         <v>41</v>
       </c>
       <c r="G7" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="H7" s="20" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="I7" s="21" t="inlineStr">
+        <v>5</v>
+      </c>
+      <c r="H7" s="19" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I7" s="20" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="J7" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K7" s="23" t="inlineStr">
-        <is>
-          <t>non responsive | pas de @media | pas de flex/grid | pas de variables CSS | police vintage</t>
+      <c r="J7" s="21" t="inlineStr">
+        <is>
+          <t>website builder 12.0.7</t>
+        </is>
+      </c>
+      <c r="K7" s="22" t="inlineStr">
+        <is>
+          <t>doctype ancien | non responsive | pas de @media | pas de flex/grid | pas de variables CSS</t>
         </is>
       </c>
     </row>
@@ -2287,13 +2287,13 @@
           <t>Nantes</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr"/>
+      <c r="D8" s="23" t="inlineStr"/>
       <c r="E8" s="8" t="inlineStr">
         <is>
           <t>44</t>
         </is>
       </c>
-      <c r="F8" s="25" t="n">
+      <c r="F8" s="26" t="n">
         <v>32</v>
       </c>
       <c r="G8" s="8" t="n">
@@ -2336,34 +2336,34 @@
           <t>Besancon</t>
         </is>
       </c>
-      <c r="D9" s="17" t="inlineStr"/>
+      <c r="D9" s="24" t="inlineStr"/>
       <c r="E9" s="18" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="F9" s="25" t="n">
+      <c r="F9" s="26" t="n">
         <v>29</v>
       </c>
       <c r="G9" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="H9" s="20" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="I9" s="20" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="J9" s="22" t="inlineStr">
+      <c r="H9" s="19" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I9" s="19" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="J9" s="21" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K9" s="23" t="inlineStr">
+      <c r="K9" s="22" t="inlineStr">
         <is>
           <t>frameset | doctype ancien | non responsive</t>
         </is>
@@ -2385,13 +2385,13 @@
           <t>Nimes</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr"/>
+      <c r="D10" s="23" t="inlineStr"/>
       <c r="E10" s="8" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="F10" s="25" t="n">
+      <c r="F10" s="26" t="n">
         <v>25</v>
       </c>
       <c r="G10" s="8" t="n">
@@ -2533,43 +2533,43 @@
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>depuy.free.fr</t>
+          <t>eco-laverie-toulouse.fr</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>SAV Depuy</t>
+          <t>ECO Laverie</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Paris</t>
-        </is>
-      </c>
-      <c r="D4" s="26" t="inlineStr">
-        <is>
-          <t>Saint Brice sous Fort (95350)</t>
+          <t>Toulouse</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>Toulouse (31000)</t>
         </is>
       </c>
       <c r="E4" s="8" t="inlineStr">
         <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="F4" s="19" t="n">
-        <v>38</v>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="F4" s="25" t="n">
+        <v>46</v>
       </c>
       <c r="G4" s="8" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H4" s="10" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
-      <c r="I4" s="10" t="inlineStr">
-        <is>
-          <t>non</t>
+      <c r="I4" s="11" t="inlineStr">
+        <is>
+          <t>oui</t>
         </is>
       </c>
       <c r="J4" s="12" t="inlineStr">
@@ -2579,83 +2579,87 @@
       </c>
       <c r="K4" s="13" t="inlineStr">
         <is>
-          <t>balises &lt;font&gt; (57) | bgcolor= | sans doctype | non responsive | images .gif</t>
+          <t>non responsive | pas de @media | pas de flex/grid | pas de variables CSS | CSS tres court (434B) | aucun radius/ombre</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="14" t="inlineStr">
         <is>
-          <t>cs2m.fr</t>
+          <t>bourges-menager-service.fr</t>
         </is>
       </c>
       <c r="B5" s="15" t="inlineStr">
         <is>
-          <t>CS2M - Cordonnerie Serrurerie</t>
+          <t>Bourges Ménager Service</t>
         </is>
       </c>
       <c r="C5" s="16" t="inlineStr">
         <is>
-          <t>Toulouse</t>
-        </is>
-      </c>
-      <c r="D5" s="17" t="inlineStr"/>
+          <t>Bourges</t>
+        </is>
+      </c>
+      <c r="D5" s="17" t="inlineStr">
+        <is>
+          <t>Bourges (18000)</t>
+        </is>
+      </c>
       <c r="E5" s="18" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>18</t>
         </is>
       </c>
       <c r="F5" s="25" t="n">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="G5" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="H5" s="20" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="I5" s="21" t="inlineStr">
+      <c r="H5" s="19" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I5" s="20" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="J5" s="22" t="inlineStr">
+      <c r="J5" s="21" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K5" s="23" t="inlineStr">
-        <is>
-          <t>non responsive | pas de @media | pas de flex/grid</t>
+      <c r="K5" s="22" t="inlineStr">
+        <is>
+          <t>non responsive | images .gif | pas de @media | pas de flex/grid | pas de variables CSS | aucun radius/ombre</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>pressingleluxembourg.com</t>
+          <t>cs2m.fr</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Le Luxembourg</t>
+          <t>CS2M - Cordonnerie Serrurerie</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Paris</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr"/>
+          <t>Toulouse</t>
+        </is>
+      </c>
+      <c r="D6" s="23" t="inlineStr"/>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="F6" s="25" t="n">
-        <v>32</v>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="F6" s="26" t="n">
+        <v>34</v>
       </c>
       <c r="G6" s="8" t="n">
         <v>5</v>
@@ -2665,9 +2669,9 @@
           <t>non</t>
         </is>
       </c>
-      <c r="I6" s="10" t="inlineStr">
-        <is>
-          <t>non</t>
+      <c r="I6" s="11" t="inlineStr">
+        <is>
+          <t>oui</t>
         </is>
       </c>
       <c r="J6" s="12" t="inlineStr">
@@ -2677,54 +2681,54 @@
       </c>
       <c r="K6" s="13" t="inlineStr">
         <is>
-          <t>non responsive | pas de @media | pas de variables CSS</t>
+          <t>non responsive | pas de @media | pas de flex/grid</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>floriansbikes.com</t>
+          <t>pressingleluxembourg.com</t>
         </is>
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>Florian's Bikes</t>
+          <t>Le Luxembourg</t>
         </is>
       </c>
       <c r="C7" s="16" t="inlineStr">
         <is>
-          <t>Toulouse</t>
-        </is>
-      </c>
-      <c r="D7" s="17" t="inlineStr"/>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="D7" s="24" t="inlineStr"/>
       <c r="E7" s="18" t="inlineStr">
         <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="F7" s="25" t="n">
+          <t>75</t>
+        </is>
+      </c>
+      <c r="F7" s="26" t="n">
         <v>32</v>
       </c>
       <c r="G7" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="H7" s="20" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="I7" s="21" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="J7" s="22" t="inlineStr">
+      <c r="H7" s="19" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I7" s="19" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="J7" s="21" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K7" s="23" t="inlineStr">
+      <c r="K7" s="22" t="inlineStr">
         <is>
           <t>non responsive | pas de @media | pas de variables CSS</t>
         </is>
@@ -2733,34 +2737,30 @@
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>autourducycle.fr</t>
+          <t>floriansbikes.com</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Autour du Cycle</t>
+          <t>Florian's Bikes</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Paris</t>
-        </is>
-      </c>
-      <c r="D8" s="26" t="inlineStr">
-        <is>
-          <t>La Varenne Saint Hilaire (94210)</t>
-        </is>
-      </c>
+          <t>Toulouse</t>
+        </is>
+      </c>
+      <c r="D8" s="23" t="inlineStr"/>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="F8" s="25" t="n">
-        <v>29</v>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="F8" s="26" t="n">
+        <v>32</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H8" s="10" t="inlineStr">
         <is>
@@ -2779,7 +2779,7 @@
       </c>
       <c r="K8" s="13" t="inlineStr">
         <is>
-          <t>balises &lt;font&gt; (11) | non responsive | police vintage</t>
+          <t>non responsive | pas de @media | pas de variables CSS</t>
         </is>
       </c>
     </row>
@@ -2799,34 +2799,34 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="D9" s="17" t="inlineStr"/>
+      <c r="D9" s="24" t="inlineStr"/>
       <c r="E9" s="18" t="inlineStr">
         <is>
           <t>75</t>
         </is>
       </c>
-      <c r="F9" s="25" t="n">
+      <c r="F9" s="26" t="n">
         <v>25</v>
       </c>
       <c r="G9" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="H9" s="20" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="I9" s="20" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="J9" s="22" t="inlineStr">
+      <c r="H9" s="19" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I9" s="19" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="J9" s="21" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K9" s="23" t="inlineStr">
+      <c r="K9" s="22" t="inlineStr">
         <is>
           <t>frameset | non responsive</t>
         </is>
@@ -2848,13 +2848,13 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr"/>
+      <c r="D10" s="23" t="inlineStr"/>
       <c r="E10" s="8" t="inlineStr">
         <is>
           <t>75</t>
         </is>
       </c>
-      <c r="F10" s="25" t="n">
+      <c r="F10" s="26" t="n">
         <v>25</v>
       </c>
       <c r="G10" s="8" t="n">

--- a/lot_02.xlsx
+++ b/lot_02.xlsx
@@ -89,14 +89,14 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00111827"/>
-      <sz val="10"/>
+      <color rgb="0092400E"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="0092400E"/>
-      <sz val="11"/>
+      <color rgb="00111827"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -182,7 +182,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -212,10 +212,13 @@
     <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -230,17 +233,14 @@
     <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -697,27 +697,23 @@
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>atlantiquegouttieres.fr</t>
+          <t>lambert-licorni.fr</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>Atlantique Gouttières</t>
+          <t>Lambert Licorni</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>La Rochelle</t>
-        </is>
-      </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>Aytré (17440)</t>
-        </is>
-      </c>
+          <t>Nancy</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr"/>
       <c r="E4" s="8" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F4" s="9" t="n">
@@ -743,99 +739,95 @@
       </c>
       <c r="K4" s="13" t="inlineStr">
         <is>
-          <t>balises &lt;font&gt; (20) | non responsive | pas de @media | pas de flex/grid | pas de variables CSS | CSS tres court (434B) | aucun radius/ombre</t>
+          <t>balises &lt;font&gt; (16) | non responsive | pas de @media | pas de flex/grid | pas de variables CSS | CSS tres court (434B) | aucun radius/ombre</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="14" t="inlineStr">
         <is>
-          <t>doussot.fr</t>
+          <t>celo-gaz.com</t>
         </is>
       </c>
       <c r="B5" s="15" t="inlineStr">
         <is>
-          <t>Doussot Service Énergie</t>
+          <t>Celo gaz</t>
         </is>
       </c>
       <c r="C5" s="16" t="inlineStr">
         <is>
-          <t>Dijon</t>
-        </is>
-      </c>
-      <c r="D5" s="17" t="inlineStr">
-        <is>
-          <t>Dijon (21000)</t>
-        </is>
-      </c>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="D5" s="17" t="inlineStr"/>
       <c r="E5" s="18" t="inlineStr">
         <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="F5" s="9" t="n">
-        <v>56</v>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="F5" s="19" t="n">
+        <v>46</v>
       </c>
       <c r="G5" s="18" t="n">
-        <v>6</v>
-      </c>
-      <c r="H5" s="19" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="I5" s="20" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="H5" s="20" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I5" s="21" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="J5" s="21" t="inlineStr">
+      <c r="J5" s="22" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K5" s="22" t="inlineStr">
-        <is>
-          <t>balises &lt;font&gt; (4) | non responsive | pas de @media | pas de flex/grid | pas de variables CSS | CSS tres court (434B) | aucun radius/ombre</t>
+      <c r="K5" s="23" t="inlineStr">
+        <is>
+          <t>non responsive | pas de @media | pas de flex/grid | pas de variables CSS | CSS tres court (434B) | aucun radius/ombre</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>lambert-licorni.fr</t>
+          <t>atelier-delaunay.fr</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Lambert Licorni</t>
+          <t>Atelier Delaunay</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Nancy</t>
-        </is>
-      </c>
-      <c r="D6" s="23" t="inlineStr"/>
+          <t>Le Havre</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr"/>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="F6" s="9" t="n">
-        <v>56</v>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="F6" s="19" t="n">
+        <v>41</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H6" s="10" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
-      <c r="I6" s="11" t="inlineStr">
-        <is>
-          <t>oui</t>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>non</t>
         </is>
       </c>
       <c r="J6" s="12" t="inlineStr">
@@ -845,19 +837,19 @@
       </c>
       <c r="K6" s="13" t="inlineStr">
         <is>
-          <t>balises &lt;font&gt; (16) | non responsive | pas de @media | pas de flex/grid | pas de variables CSS | CSS tres court (434B) | aucun radius/ombre</t>
+          <t>layout en tableaux (25) | bgcolor= | doctype ancien | non responsive | &lt;br&gt; en masse</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>celo-gaz.com</t>
+          <t>h4b.fr</t>
         </is>
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>Celo gaz</t>
+          <t>Henri De Quatres Barbes</t>
         </is>
       </c>
       <c r="C7" s="16" t="inlineStr">
@@ -865,75 +857,79 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="D7" s="24" t="inlineStr"/>
+      <c r="D7" s="24" t="inlineStr">
+        <is>
+          <t>Boulogne Billancourt (92100)</t>
+        </is>
+      </c>
       <c r="E7" s="18" t="inlineStr">
         <is>
           <t>75</t>
         </is>
       </c>
-      <c r="F7" s="25" t="n">
-        <v>46</v>
+      <c r="F7" s="19" t="n">
+        <v>39</v>
       </c>
       <c r="G7" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="H7" s="19" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="I7" s="20" t="inlineStr">
+      <c r="H7" s="20" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I7" s="21" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="J7" s="21" t="inlineStr">
+      <c r="J7" s="22" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K7" s="22" t="inlineStr">
-        <is>
-          <t>non responsive | pas de @media | pas de flex/grid | pas de variables CSS | CSS tres court (434B) | aucun radius/ombre</t>
+      <c r="K7" s="23" t="inlineStr">
+        <is>
+          <t>doctype ancien | non responsive | images .gif | pas de @media | pas de variables CSS</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>atelier-delaunay.fr</t>
+          <t>begrand.fr</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Atelier Delaunay</t>
+          <t>Entreprise Begrand</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Le Havre</t>
-        </is>
-      </c>
-      <c r="D8" s="23" t="inlineStr"/>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr"/>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>75</t>
         </is>
       </c>
       <c r="F8" s="25" t="n">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H8" s="10" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
-      <c r="I8" s="10" t="inlineStr">
-        <is>
-          <t>non</t>
+      <c r="I8" s="11" t="inlineStr">
+        <is>
+          <t>oui</t>
         </is>
       </c>
       <c r="J8" s="12" t="inlineStr">
@@ -943,95 +939,99 @@
       </c>
       <c r="K8" s="13" t="inlineStr">
         <is>
-          <t>layout en tableaux (25) | bgcolor= | doctype ancien | non responsive | &lt;br&gt; en masse</t>
+          <t>balises &lt;font&gt; (3) | doctype ancien | non responsive | document.write</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>begrand.fr</t>
+          <t>brunelli.fr</t>
         </is>
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>Entreprise Begrand</t>
+          <t>Brunelli</t>
         </is>
       </c>
       <c r="C9" s="16" t="inlineStr">
         <is>
-          <t>Paris</t>
-        </is>
-      </c>
-      <c r="D9" s="24" t="inlineStr"/>
+          <t>Nancy</t>
+        </is>
+      </c>
+      <c r="D9" s="17" t="inlineStr"/>
       <c r="E9" s="18" t="inlineStr">
         <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="F9" s="26" t="n">
-        <v>33</v>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="F9" s="25" t="n">
+        <v>29</v>
       </c>
       <c r="G9" s="18" t="n">
-        <v>6</v>
-      </c>
-      <c r="H9" s="19" t="inlineStr">
+        <v>8</v>
+      </c>
+      <c r="H9" s="20" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
       <c r="I9" s="20" t="inlineStr">
         <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="J9" s="21" t="inlineStr">
+          <t>non</t>
+        </is>
+      </c>
+      <c r="J9" s="22" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K9" s="22" t="inlineStr">
-        <is>
-          <t>balises &lt;font&gt; (3) | doctype ancien | non responsive | document.write</t>
+      <c r="K9" s="23" t="inlineStr">
+        <is>
+          <t>frameset | doctype ancien | non responsive</t>
         </is>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>brunelli.fr</t>
+          <t>alazard-sas.com</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Brunelli</t>
+          <t>Alazard</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Nancy</t>
-        </is>
-      </c>
-      <c r="D10" s="23" t="inlineStr"/>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="D10" s="26" t="inlineStr">
+        <is>
+          <t>LENTREPRISE (94500)</t>
+        </is>
+      </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="F10" s="26" t="n">
+          <t>75</t>
+        </is>
+      </c>
+      <c r="F10" s="25" t="n">
         <v>29</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H10" s="10" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
-      <c r="I10" s="10" t="inlineStr">
-        <is>
-          <t>non</t>
+      <c r="I10" s="11" t="inlineStr">
+        <is>
+          <t>oui</t>
         </is>
       </c>
       <c r="J10" s="12" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="K10" s="13" t="inlineStr">
         <is>
-          <t>frameset | doctype ancien | non responsive</t>
+          <t>non responsive | pas de @media</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
           <t>Nantes</t>
         </is>
       </c>
-      <c r="D4" s="23" t="inlineStr"/>
+      <c r="D4" s="7" t="inlineStr"/>
       <c r="E4" s="8" t="inlineStr">
         <is>
           <t>44</t>
@@ -1222,7 +1222,7 @@
           <t>Lyon</t>
         </is>
       </c>
-      <c r="D5" s="24" t="inlineStr"/>
+      <c r="D5" s="17" t="inlineStr"/>
       <c r="E5" s="18" t="inlineStr">
         <is>
           <t>69</t>
@@ -1234,22 +1234,22 @@
       <c r="G5" s="18" t="n">
         <v>6</v>
       </c>
-      <c r="H5" s="19" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="I5" s="20" t="inlineStr">
+      <c r="H5" s="20" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I5" s="21" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="J5" s="21" t="inlineStr">
+      <c r="J5" s="22" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K5" s="22" t="inlineStr">
+      <c r="K5" s="23" t="inlineStr">
         <is>
           <t>balises &lt;font&gt; (48) | non responsive | pas de @media | pas de flex/grid | pas de variables CSS | CSS tres court (434B) | aucun radius/ombre</t>
         </is>
@@ -1271,7 +1271,7 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="D6" s="23" t="inlineStr"/>
+      <c r="D6" s="7" t="inlineStr"/>
       <c r="E6" s="8" t="inlineStr">
         <is>
           <t>75</t>
@@ -1320,34 +1320,34 @@
           <t>Lyon</t>
         </is>
       </c>
-      <c r="D7" s="24" t="inlineStr"/>
+      <c r="D7" s="17" t="inlineStr"/>
       <c r="E7" s="18" t="inlineStr">
         <is>
           <t>69</t>
         </is>
       </c>
-      <c r="F7" s="25" t="n">
+      <c r="F7" s="19" t="n">
         <v>46</v>
       </c>
       <c r="G7" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="H7" s="19" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="I7" s="20" t="inlineStr">
+      <c r="H7" s="20" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I7" s="21" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="J7" s="21" t="inlineStr">
+      <c r="J7" s="22" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K7" s="22" t="inlineStr">
+      <c r="K7" s="23" t="inlineStr">
         <is>
           <t>non responsive | pas de @media | pas de flex/grid | pas de variables CSS | CSS tres court (434B) | aucun radius/ombre</t>
         </is>
@@ -1369,13 +1369,13 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="D8" s="23" t="inlineStr"/>
+      <c r="D8" s="7" t="inlineStr"/>
       <c r="E8" s="8" t="inlineStr">
         <is>
           <t>75</t>
         </is>
       </c>
-      <c r="F8" s="25" t="n">
+      <c r="F8" s="19" t="n">
         <v>46</v>
       </c>
       <c r="G8" s="8" t="n">
@@ -1418,34 +1418,34 @@
           <t>Rouen</t>
         </is>
       </c>
-      <c r="D9" s="24" t="inlineStr"/>
+      <c r="D9" s="17" t="inlineStr"/>
       <c r="E9" s="18" t="inlineStr">
         <is>
           <t>76</t>
         </is>
       </c>
-      <c r="F9" s="25" t="n">
+      <c r="F9" s="19" t="n">
         <v>42</v>
       </c>
       <c r="G9" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="H9" s="19" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="I9" s="20" t="inlineStr">
+      <c r="H9" s="20" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I9" s="21" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="J9" s="21" t="inlineStr">
+      <c r="J9" s="22" t="inlineStr">
         <is>
           <t>webacappella 4.6.18 free (win)</t>
         </is>
       </c>
-      <c r="K9" s="22" t="inlineStr">
+      <c r="K9" s="23" t="inlineStr">
         <is>
           <t>doctype ancien | non responsive | document.write | pas de @media | pas de flex/grid</t>
         </is>
@@ -1467,13 +1467,13 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="D10" s="23" t="inlineStr"/>
+      <c r="D10" s="7" t="inlineStr"/>
       <c r="E10" s="8" t="inlineStr">
         <is>
           <t>75</t>
         </is>
       </c>
-      <c r="F10" s="25" t="n">
+      <c r="F10" s="19" t="n">
         <v>41</v>
       </c>
       <c r="G10" s="8" t="n">
@@ -1615,31 +1615,27 @@
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>friteriedumynck.fr</t>
+          <t>bouilloncapitole.fr</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>Friterie du Mynck</t>
+          <t>Le Bouillon Capitole</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
-        </is>
-      </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>Dunkerque (59140)</t>
-        </is>
-      </c>
+          <t>Toulouse</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr"/>
       <c r="E4" s="8" t="inlineStr">
         <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="F4" s="9" t="n">
-        <v>56</v>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="n">
+        <v>42</v>
       </c>
       <c r="G4" s="8" t="n">
         <v>6</v>
@@ -1661,95 +1657,95 @@
       </c>
       <c r="K4" s="13" t="inlineStr">
         <is>
-          <t>balises &lt;font&gt; (1) | non responsive | pas de @media | pas de flex/grid | pas de variables CSS | CSS tres court (434B) | aucun radius/ombre</t>
+          <t>&lt;center&gt; | non responsive | pas de @media | pas de flex/grid | pas de variables CSS</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="14" t="inlineStr">
         <is>
-          <t>bouilloncapitole.fr</t>
+          <t>surlepouce.libanais.free.fr</t>
         </is>
       </c>
       <c r="B5" s="15" t="inlineStr">
         <is>
-          <t>Le Bouillon Capitole</t>
+          <t>Sur le Pouce</t>
         </is>
       </c>
       <c r="C5" s="16" t="inlineStr">
         <is>
-          <t>Toulouse</t>
-        </is>
-      </c>
-      <c r="D5" s="24" t="inlineStr"/>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="D5" s="17" t="inlineStr"/>
       <c r="E5" s="18" t="inlineStr">
         <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="F5" s="25" t="n">
-        <v>42</v>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="F5" s="19" t="n">
+        <v>39</v>
       </c>
       <c r="G5" s="18" t="n">
-        <v>6</v>
-      </c>
-      <c r="H5" s="19" t="inlineStr">
+        <v>8</v>
+      </c>
+      <c r="H5" s="20" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
       <c r="I5" s="20" t="inlineStr">
         <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="J5" s="21" t="inlineStr">
+          <t>non</t>
+        </is>
+      </c>
+      <c r="J5" s="22" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K5" s="22" t="inlineStr">
-        <is>
-          <t>&lt;center&gt; | non responsive | pas de @media | pas de flex/grid | pas de variables CSS</t>
+      <c r="K5" s="23" t="inlineStr">
+        <is>
+          <t>layout en tableaux (8) | bgcolor= | sans doctype | non responsive</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>surlepouce.libanais.free.fr</t>
+          <t>gindalle.fr</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Sur le Pouce</t>
+          <t>Gin Dalle</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Paris</t>
-        </is>
-      </c>
-      <c r="D6" s="23" t="inlineStr"/>
+          <t>Toulouse</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr"/>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="F6" s="25" t="n">
+          <t>31</t>
+        </is>
+      </c>
+      <c r="F6" s="19" t="n">
         <v>39</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H6" s="10" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
-      <c r="I6" s="10" t="inlineStr">
-        <is>
-          <t>non</t>
+      <c r="I6" s="11" t="inlineStr">
+        <is>
+          <t>oui</t>
         </is>
       </c>
       <c r="J6" s="12" t="inlineStr">
@@ -1759,19 +1755,19 @@
       </c>
       <c r="K6" s="13" t="inlineStr">
         <is>
-          <t>layout en tableaux (8) | bgcolor= | sans doctype | non responsive</t>
+          <t>layout en tableaux (4) | bgcolor= | sans doctype | non responsive</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>gindalle.fr</t>
+          <t>toulousefruitsdemer.fr</t>
         </is>
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>Gin Dalle</t>
+          <t>La Cabane</t>
         </is>
       </c>
       <c r="C7" s="16" t="inlineStr">
@@ -1779,134 +1775,138 @@
           <t>Toulouse</t>
         </is>
       </c>
-      <c r="D7" s="24" t="inlineStr"/>
+      <c r="D7" s="17" t="inlineStr"/>
       <c r="E7" s="18" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="F7" s="25" t="n">
-        <v>39</v>
+      <c r="F7" s="19" t="n">
+        <v>38</v>
       </c>
       <c r="G7" s="18" t="n">
-        <v>6</v>
-      </c>
-      <c r="H7" s="19" t="inlineStr">
+        <v>8</v>
+      </c>
+      <c r="H7" s="20" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
       <c r="I7" s="20" t="inlineStr">
         <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="J7" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K7" s="22" t="inlineStr">
-        <is>
-          <t>layout en tableaux (4) | bgcolor= | sans doctype | non responsive</t>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="J7" s="22" t="inlineStr">
+        <is>
+          <t>wordpress 3.7.41</t>
+        </is>
+      </c>
+      <c r="K7" s="23" t="inlineStr">
+        <is>
+          <t>doctype ancien | non responsive | pas de @media | pas de flex/grid</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>toulousefruitsdemer.fr</t>
+          <t>crocknpizz.fr</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>La Cabane</t>
+          <t>C'rock n'pizz</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Toulouse</t>
-        </is>
-      </c>
-      <c r="D8" s="23" t="inlineStr"/>
+          <t>Lyon</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr"/>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="F8" s="25" t="n">
-        <v>38</v>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="F8" s="19" t="n">
+        <v>37</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H8" s="10" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
-      <c r="I8" s="10" t="inlineStr">
-        <is>
-          <t>non</t>
+      <c r="I8" s="11" t="inlineStr">
+        <is>
+          <t>oui</t>
         </is>
       </c>
       <c r="J8" s="12" t="inlineStr">
         <is>
-          <t>wordpress 3.7.41</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K8" s="13" t="inlineStr">
         <is>
-          <t>doctype ancien | non responsive | pas de @media | pas de flex/grid</t>
+          <t>layout en tableaux (95) | &lt;center&gt; | non responsive | &lt;br&gt; en masse</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>crocknpizz.fr</t>
+          <t>bistrobest.fr</t>
         </is>
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>C'rock n'pizz</t>
+          <t>Bistro Best</t>
         </is>
       </c>
       <c r="C9" s="16" t="inlineStr">
         <is>
-          <t>Lyon</t>
-        </is>
-      </c>
-      <c r="D9" s="24" t="inlineStr"/>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="D9" s="24" t="inlineStr">
+        <is>
+          <t>Marly (78160)</t>
+        </is>
+      </c>
       <c r="E9" s="18" t="inlineStr">
         <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="F9" s="25" t="n">
+          <t>75</t>
+        </is>
+      </c>
+      <c r="F9" s="19" t="n">
         <v>37</v>
       </c>
       <c r="G9" s="18" t="n">
-        <v>6</v>
-      </c>
-      <c r="H9" s="19" t="inlineStr">
+        <v>5</v>
+      </c>
+      <c r="H9" s="20" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
       <c r="I9" s="20" t="inlineStr">
         <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="J9" s="21" t="inlineStr">
+          <t>non</t>
+        </is>
+      </c>
+      <c r="J9" s="22" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K9" s="22" t="inlineStr">
-        <is>
-          <t>layout en tableaux (95) | &lt;center&gt; | non responsive | &lt;br&gt; en masse</t>
+      <c r="K9" s="23" t="inlineStr">
+        <is>
+          <t>non responsive | document.write | pas de @media | police vintage</t>
         </is>
       </c>
     </row>
@@ -1926,13 +1926,13 @@
           <t>Lille</t>
         </is>
       </c>
-      <c r="D10" s="23" t="inlineStr"/>
+      <c r="D10" s="7" t="inlineStr"/>
       <c r="E10" s="8" t="inlineStr">
         <is>
           <t>59</t>
         </is>
       </c>
-      <c r="F10" s="25" t="n">
+      <c r="F10" s="19" t="n">
         <v>37</v>
       </c>
       <c r="G10" s="8" t="n">
@@ -2087,7 +2087,7 @@
           <t>Lyon</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D4" s="26" t="inlineStr">
         <is>
           <t>Villeurbanne (69100)</t>
         </is>
@@ -2140,7 +2140,7 @@
           <t>Toulouse</t>
         </is>
       </c>
-      <c r="D5" s="24" t="inlineStr"/>
+      <c r="D5" s="17" t="inlineStr"/>
       <c r="E5" s="18" t="inlineStr">
         <is>
           <t>31</t>
@@ -2152,22 +2152,22 @@
       <c r="G5" s="18" t="n">
         <v>6</v>
       </c>
-      <c r="H5" s="19" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="I5" s="20" t="inlineStr">
+      <c r="H5" s="20" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I5" s="21" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="J5" s="21" t="inlineStr">
+      <c r="J5" s="22" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K5" s="22" t="inlineStr">
+      <c r="K5" s="23" t="inlineStr">
         <is>
           <t>balises &lt;font&gt; (4) | non responsive | pas de @media | pas de flex/grid | pas de variables CSS | CSS tres court (434B) | aucun radius/ombre</t>
         </is>
@@ -2189,13 +2189,13 @@
           <t>Lyon</t>
         </is>
       </c>
-      <c r="D6" s="23" t="inlineStr"/>
+      <c r="D6" s="7" t="inlineStr"/>
       <c r="E6" s="8" t="inlineStr">
         <is>
           <t>69</t>
         </is>
       </c>
-      <c r="F6" s="25" t="n">
+      <c r="F6" s="19" t="n">
         <v>44</v>
       </c>
       <c r="G6" s="8" t="n">
@@ -2238,34 +2238,34 @@
           <t>Rennes</t>
         </is>
       </c>
-      <c r="D7" s="24" t="inlineStr"/>
+      <c r="D7" s="17" t="inlineStr"/>
       <c r="E7" s="18" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="F7" s="25" t="n">
+      <c r="F7" s="19" t="n">
         <v>41</v>
       </c>
       <c r="G7" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="H7" s="19" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="I7" s="20" t="inlineStr">
+      <c r="H7" s="20" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I7" s="21" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="J7" s="21" t="inlineStr">
+      <c r="J7" s="22" t="inlineStr">
         <is>
           <t>website builder 12.0.7</t>
         </is>
       </c>
-      <c r="K7" s="22" t="inlineStr">
+      <c r="K7" s="23" t="inlineStr">
         <is>
           <t>doctype ancien | non responsive | pas de @media | pas de flex/grid | pas de variables CSS</t>
         </is>
@@ -2287,13 +2287,13 @@
           <t>Nantes</t>
         </is>
       </c>
-      <c r="D8" s="23" t="inlineStr"/>
+      <c r="D8" s="7" t="inlineStr"/>
       <c r="E8" s="8" t="inlineStr">
         <is>
           <t>44</t>
         </is>
       </c>
-      <c r="F8" s="26" t="n">
+      <c r="F8" s="25" t="n">
         <v>32</v>
       </c>
       <c r="G8" s="8" t="n">
@@ -2336,34 +2336,34 @@
           <t>Besancon</t>
         </is>
       </c>
-      <c r="D9" s="24" t="inlineStr"/>
+      <c r="D9" s="17" t="inlineStr"/>
       <c r="E9" s="18" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="F9" s="26" t="n">
+      <c r="F9" s="25" t="n">
         <v>29</v>
       </c>
       <c r="G9" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="H9" s="19" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="I9" s="19" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="J9" s="21" t="inlineStr">
+      <c r="H9" s="20" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I9" s="20" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="J9" s="22" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K9" s="22" t="inlineStr">
+      <c r="K9" s="23" t="inlineStr">
         <is>
           <t>frameset | doctype ancien | non responsive</t>
         </is>
@@ -2385,13 +2385,13 @@
           <t>Nimes</t>
         </is>
       </c>
-      <c r="D10" s="23" t="inlineStr"/>
+      <c r="D10" s="7" t="inlineStr"/>
       <c r="E10" s="8" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="F10" s="26" t="n">
+      <c r="F10" s="25" t="n">
         <v>25</v>
       </c>
       <c r="G10" s="8" t="n">
@@ -2533,43 +2533,43 @@
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>eco-laverie-toulouse.fr</t>
+          <t>depuy.free.fr</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>ECO Laverie</t>
+          <t>SAV Depuy</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Toulouse</t>
-        </is>
-      </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>Toulouse (31000)</t>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="D4" s="26" t="inlineStr">
+        <is>
+          <t>Saint Brice sous Fort (95350)</t>
         </is>
       </c>
       <c r="E4" s="8" t="inlineStr">
         <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="F4" s="25" t="n">
-        <v>46</v>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="n">
+        <v>38</v>
       </c>
       <c r="G4" s="8" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H4" s="10" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
-      <c r="I4" s="11" t="inlineStr">
-        <is>
-          <t>oui</t>
+      <c r="I4" s="10" t="inlineStr">
+        <is>
+          <t>non</t>
         </is>
       </c>
       <c r="J4" s="12" t="inlineStr">
@@ -2579,87 +2579,83 @@
       </c>
       <c r="K4" s="13" t="inlineStr">
         <is>
-          <t>non responsive | pas de @media | pas de flex/grid | pas de variables CSS | CSS tres court (434B) | aucun radius/ombre</t>
+          <t>balises &lt;font&gt; (57) | bgcolor= | sans doctype | non responsive | images .gif</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="14" t="inlineStr">
         <is>
-          <t>bourges-menager-service.fr</t>
+          <t>cs2m.fr</t>
         </is>
       </c>
       <c r="B5" s="15" t="inlineStr">
         <is>
-          <t>Bourges Ménager Service</t>
+          <t>CS2M - Cordonnerie Serrurerie</t>
         </is>
       </c>
       <c r="C5" s="16" t="inlineStr">
         <is>
-          <t>Bourges</t>
-        </is>
-      </c>
-      <c r="D5" s="17" t="inlineStr">
-        <is>
-          <t>Bourges (18000)</t>
-        </is>
-      </c>
+          <t>Toulouse</t>
+        </is>
+      </c>
+      <c r="D5" s="17" t="inlineStr"/>
       <c r="E5" s="18" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>31</t>
         </is>
       </c>
       <c r="F5" s="25" t="n">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="G5" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="H5" s="19" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="I5" s="20" t="inlineStr">
+      <c r="H5" s="20" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I5" s="21" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="J5" s="21" t="inlineStr">
+      <c r="J5" s="22" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K5" s="22" t="inlineStr">
-        <is>
-          <t>non responsive | images .gif | pas de @media | pas de flex/grid | pas de variables CSS | aucun radius/ombre</t>
+      <c r="K5" s="23" t="inlineStr">
+        <is>
+          <t>non responsive | pas de @media | pas de flex/grid</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>cs2m.fr</t>
+          <t>pressingleluxembourg.com</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>CS2M - Cordonnerie Serrurerie</t>
+          <t>Le Luxembourg</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Toulouse</t>
-        </is>
-      </c>
-      <c r="D6" s="23" t="inlineStr"/>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr"/>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="F6" s="26" t="n">
-        <v>34</v>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="F6" s="25" t="n">
+        <v>32</v>
       </c>
       <c r="G6" s="8" t="n">
         <v>5</v>
@@ -2669,9 +2665,9 @@
           <t>non</t>
         </is>
       </c>
-      <c r="I6" s="11" t="inlineStr">
-        <is>
-          <t>oui</t>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>non</t>
         </is>
       </c>
       <c r="J6" s="12" t="inlineStr">
@@ -2681,54 +2677,54 @@
       </c>
       <c r="K6" s="13" t="inlineStr">
         <is>
-          <t>non responsive | pas de @media | pas de flex/grid</t>
+          <t>non responsive | pas de @media | pas de variables CSS</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>pressingleluxembourg.com</t>
+          <t>floriansbikes.com</t>
         </is>
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>Le Luxembourg</t>
+          <t>Florian's Bikes</t>
         </is>
       </c>
       <c r="C7" s="16" t="inlineStr">
         <is>
-          <t>Paris</t>
-        </is>
-      </c>
-      <c r="D7" s="24" t="inlineStr"/>
+          <t>Toulouse</t>
+        </is>
+      </c>
+      <c r="D7" s="17" t="inlineStr"/>
       <c r="E7" s="18" t="inlineStr">
         <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="F7" s="26" t="n">
+          <t>31</t>
+        </is>
+      </c>
+      <c r="F7" s="25" t="n">
         <v>32</v>
       </c>
       <c r="G7" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="H7" s="19" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="I7" s="19" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="J7" s="21" t="inlineStr">
+      <c r="H7" s="20" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I7" s="21" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J7" s="22" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K7" s="22" t="inlineStr">
+      <c r="K7" s="23" t="inlineStr">
         <is>
           <t>non responsive | pas de @media | pas de variables CSS</t>
         </is>
@@ -2737,30 +2733,34 @@
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>floriansbikes.com</t>
+          <t>autourducycle.fr</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Florian's Bikes</t>
+          <t>Autour du Cycle</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Toulouse</t>
-        </is>
-      </c>
-      <c r="D8" s="23" t="inlineStr"/>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="D8" s="26" t="inlineStr">
+        <is>
+          <t>La Varenne Saint Hilaire (94210)</t>
+        </is>
+      </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="F8" s="26" t="n">
-        <v>32</v>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="F8" s="25" t="n">
+        <v>29</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H8" s="10" t="inlineStr">
         <is>
@@ -2779,7 +2779,7 @@
       </c>
       <c r="K8" s="13" t="inlineStr">
         <is>
-          <t>non responsive | pas de @media | pas de variables CSS</t>
+          <t>balises &lt;font&gt; (11) | non responsive | police vintage</t>
         </is>
       </c>
     </row>
@@ -2799,34 +2799,34 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="D9" s="24" t="inlineStr"/>
+      <c r="D9" s="17" t="inlineStr"/>
       <c r="E9" s="18" t="inlineStr">
         <is>
           <t>75</t>
         </is>
       </c>
-      <c r="F9" s="26" t="n">
+      <c r="F9" s="25" t="n">
         <v>25</v>
       </c>
       <c r="G9" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="H9" s="19" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="I9" s="19" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="J9" s="21" t="inlineStr">
+      <c r="H9" s="20" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I9" s="20" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="J9" s="22" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K9" s="22" t="inlineStr">
+      <c r="K9" s="23" t="inlineStr">
         <is>
           <t>frameset | non responsive</t>
         </is>
@@ -2848,13 +2848,13 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="D10" s="23" t="inlineStr"/>
+      <c r="D10" s="7" t="inlineStr"/>
       <c r="E10" s="8" t="inlineStr">
         <is>
           <t>75</t>
         </is>
       </c>
-      <c r="F10" s="26" t="n">
+      <c r="F10" s="25" t="n">
         <v>25</v>
       </c>
       <c r="G10" s="8" t="n">

--- a/lot_02.xlsx
+++ b/lot_02.xlsx
@@ -212,7 +212,7 @@
     <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -233,14 +233,14 @@
     <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -746,12 +746,12 @@
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="14" t="inlineStr">
         <is>
-          <t>celo-gaz.com</t>
+          <t>gilsol.com</t>
         </is>
       </c>
       <c r="B5" s="15" t="inlineStr">
         <is>
-          <t>Celo gaz</t>
+          <t>Gilsol</t>
         </is>
       </c>
       <c r="C5" s="16" t="inlineStr">
@@ -759,7 +759,11 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="D5" s="17" t="inlineStr"/>
+      <c r="D5" s="17" t="inlineStr">
+        <is>
+          <t>Suresnes (92150)</t>
+        </is>
+      </c>
       <c r="E5" s="18" t="inlineStr">
         <is>
           <t>75</t>
@@ -795,39 +799,43 @@
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>atelier-delaunay.fr</t>
+          <t>fjdm.fr</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Atelier Delaunay</t>
+          <t>F.J.D.M.</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Le Havre</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr"/>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="D6" s="24" t="inlineStr">
+        <is>
+          <t>Viroflay (78220)</t>
+        </is>
+      </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>75</t>
         </is>
       </c>
       <c r="F6" s="19" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H6" s="10" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
-      <c r="I6" s="10" t="inlineStr">
-        <is>
-          <t>non</t>
+      <c r="I6" s="11" t="inlineStr">
+        <is>
+          <t>oui</t>
         </is>
       </c>
       <c r="J6" s="12" t="inlineStr">
@@ -837,38 +845,38 @@
       </c>
       <c r="K6" s="13" t="inlineStr">
         <is>
-          <t>layout en tableaux (25) | bgcolor= | doctype ancien | non responsive | &lt;br&gt; en masse</t>
+          <t>non responsive | pas de @media | pas de flex/grid | pas de variables CSS | CSS tres court (434B) | aucun radius/ombre</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>h4b.fr</t>
+          <t>entreprisedelvigne.site-solocal.com</t>
         </is>
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>Henri De Quatres Barbes</t>
+          <t>Delvigne</t>
         </is>
       </c>
       <c r="C7" s="16" t="inlineStr">
         <is>
-          <t>Paris</t>
-        </is>
-      </c>
-      <c r="D7" s="24" t="inlineStr">
-        <is>
-          <t>Boulogne Billancourt (92100)</t>
+          <t>Tours</t>
+        </is>
+      </c>
+      <c r="D7" s="17" t="inlineStr">
+        <is>
+          <t>Saint-Avertin (37550)</t>
         </is>
       </c>
       <c r="E7" s="18" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>37</t>
         </is>
       </c>
       <c r="F7" s="19" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="G7" s="18" t="n">
         <v>3</v>
@@ -890,37 +898,41 @@
       </c>
       <c r="K7" s="23" t="inlineStr">
         <is>
-          <t>doctype ancien | non responsive | images .gif | pas de @media | pas de variables CSS</t>
+          <t>non responsive | pas de @media | pas de flex/grid | pas de variables CSS | CSS tres court (434B) | aucun radius/ombre</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>begrand.fr</t>
+          <t>electricite-hertzog.fr</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Entreprise Begrand</t>
+          <t>Electricité Hertzog Daniel</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Paris</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr"/>
+          <t>Strasbourg</t>
+        </is>
+      </c>
+      <c r="D8" s="24" t="inlineStr">
+        <is>
+          <t>Schiltigheim (67300)</t>
+        </is>
+      </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="F8" s="25" t="n">
-        <v>33</v>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="F8" s="19" t="n">
+        <v>46</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H8" s="10" t="inlineStr">
         <is>
@@ -939,46 +951,46 @@
       </c>
       <c r="K8" s="13" t="inlineStr">
         <is>
-          <t>balises &lt;font&gt; (3) | doctype ancien | non responsive | document.write</t>
+          <t>non responsive | pas de @media | pas de flex/grid | pas de variables CSS | CSS tres court (434B) | aucun radius/ombre</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>brunelli.fr</t>
+          <t>econhome.fr</t>
         </is>
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>Brunelli</t>
+          <t>Eco'n home</t>
         </is>
       </c>
       <c r="C9" s="16" t="inlineStr">
         <is>
-          <t>Nancy</t>
-        </is>
-      </c>
-      <c r="D9" s="17" t="inlineStr"/>
+          <t>Limoges</t>
+        </is>
+      </c>
+      <c r="D9" s="25" t="inlineStr"/>
       <c r="E9" s="18" t="inlineStr">
         <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="F9" s="25" t="n">
-        <v>29</v>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="F9" s="19" t="n">
+        <v>37</v>
       </c>
       <c r="G9" s="18" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H9" s="20" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
-      <c r="I9" s="20" t="inlineStr">
-        <is>
-          <t>non</t>
+      <c r="I9" s="21" t="inlineStr">
+        <is>
+          <t>oui</t>
         </is>
       </c>
       <c r="J9" s="22" t="inlineStr">
@@ -988,7 +1000,7 @@
       </c>
       <c r="K9" s="23" t="inlineStr">
         <is>
-          <t>frameset | doctype ancien | non responsive</t>
+          <t>non responsive | pas de @media | pas de flex/grid | pas de variables CSS</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1020,7 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="D10" s="26" t="inlineStr">
+      <c r="D10" s="24" t="inlineStr">
         <is>
           <t>LENTREPRISE (94500)</t>
         </is>
@@ -1018,7 +1030,7 @@
           <t>75</t>
         </is>
       </c>
-      <c r="F10" s="25" t="n">
+      <c r="F10" s="26" t="n">
         <v>29</v>
       </c>
       <c r="G10" s="8" t="n">
@@ -1160,30 +1172,30 @@
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>auxsecretsdubien-etre.com</t>
+          <t>magalo.site-solocal.com</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>Aux secrets du bien-être</t>
+          <t>L’Atelier By Marina</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Bordeaux</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr"/>
       <c r="E4" s="8" t="inlineStr">
         <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="F4" s="9" t="n">
-        <v>56</v>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="n">
+        <v>46</v>
       </c>
       <c r="G4" s="8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H4" s="10" t="inlineStr">
         <is>
@@ -1202,37 +1214,37 @@
       </c>
       <c r="K4" s="13" t="inlineStr">
         <is>
-          <t>balises &lt;font&gt; (19) | non responsive | pas de @media | pas de flex/grid | pas de variables CSS | CSS tres court (434B) | aucun radius/ombre</t>
+          <t>non responsive | pas de @media | pas de flex/grid | pas de variables CSS | CSS tres court (434B) | aucun radius/ombre</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="14" t="inlineStr">
         <is>
-          <t>bc-coiffure-oullins.fr</t>
+          <t>lavillasaintmarc.com</t>
         </is>
       </c>
       <c r="B5" s="15" t="inlineStr">
         <is>
-          <t>BC Coiffure</t>
+          <t>La Villa Saint-Marc</t>
         </is>
       </c>
       <c r="C5" s="16" t="inlineStr">
         <is>
-          <t>Lyon</t>
-        </is>
-      </c>
-      <c r="D5" s="17" t="inlineStr"/>
+          <t>Rouen</t>
+        </is>
+      </c>
+      <c r="D5" s="25" t="inlineStr"/>
       <c r="E5" s="18" t="inlineStr">
         <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="F5" s="9" t="n">
-        <v>56</v>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="F5" s="19" t="n">
+        <v>42</v>
       </c>
       <c r="G5" s="18" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H5" s="20" t="inlineStr">
         <is>
@@ -1246,42 +1258,46 @@
       </c>
       <c r="J5" s="22" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>webacappella 4.6.18 free (win)</t>
         </is>
       </c>
       <c r="K5" s="23" t="inlineStr">
         <is>
-          <t>balises &lt;font&gt; (48) | non responsive | pas de @media | pas de flex/grid | pas de variables CSS | CSS tres court (434B) | aucun radius/ombre</t>
+          <t>doctype ancien | non responsive | document.write | pas de @media | pas de flex/grid</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>bzenthaiparis.com</t>
+          <t>claudiafeedessoins.fr</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>B Zen Spa</t>
+          <t>Salon de beauté Claudia</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Paris</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr"/>
+          <t>Strasbourg</t>
+        </is>
+      </c>
+      <c r="D6" s="24" t="inlineStr">
+        <is>
+          <t>Ostwald (67540)</t>
+        </is>
+      </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="F6" s="9" t="n">
-        <v>56</v>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="F6" s="19" t="n">
+        <v>37</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H6" s="10" t="inlineStr">
         <is>
@@ -1300,19 +1316,19 @@
       </c>
       <c r="K6" s="13" t="inlineStr">
         <is>
-          <t>balises &lt;font&gt; (2) | non responsive | pas de @media | pas de flex/grid | pas de variables CSS | CSS tres court (434B) | aucun radius/ombre</t>
+          <t>non responsive | pas de @media | pas de flex/grid | pas de variables CSS</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>amazen-spa.fr</t>
+          <t>elistyl-lyon8.fr</t>
         </is>
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>Amazen</t>
+          <t>Elistyl'</t>
         </is>
       </c>
       <c r="C7" s="16" t="inlineStr">
@@ -1320,21 +1336,21 @@
           <t>Lyon</t>
         </is>
       </c>
-      <c r="D7" s="17" t="inlineStr"/>
+      <c r="D7" s="25" t="inlineStr"/>
       <c r="E7" s="18" t="inlineStr">
         <is>
           <t>69</t>
         </is>
       </c>
       <c r="F7" s="19" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="G7" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="H7" s="20" t="inlineStr">
-        <is>
-          <t>non</t>
+        <v>2</v>
+      </c>
+      <c r="H7" s="21" t="inlineStr">
+        <is>
+          <t>oui</t>
         </is>
       </c>
       <c r="I7" s="21" t="inlineStr">
@@ -1349,41 +1365,41 @@
       </c>
       <c r="K7" s="23" t="inlineStr">
         <is>
-          <t>non responsive | pas de @media | pas de flex/grid | pas de variables CSS | CSS tres court (434B) | aucun radius/ombre</t>
+          <t>layout en tableaux (3) | pas de @media | pas de flex/grid | aucun radius/ombre</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>carocoiff.site-solocal.com</t>
+          <t>lionltatouage.fr</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Caro Coiff</t>
+          <t>lion'l tatouage</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Belfort</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr"/>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="F8" s="19" t="n">
-        <v>46</v>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="F8" s="26" t="n">
+        <v>31</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="H8" s="10" t="inlineStr">
-        <is>
-          <t>non</t>
+        <v>2</v>
+      </c>
+      <c r="H8" s="11" t="inlineStr">
+        <is>
+          <t>oui</t>
         </is>
       </c>
       <c r="I8" s="11" t="inlineStr">
@@ -1393,42 +1409,46 @@
       </c>
       <c r="J8" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>powered by wpbakery page builder - drag and drop page builde</t>
         </is>
       </c>
       <c r="K8" s="13" t="inlineStr">
         <is>
-          <t>non responsive | pas de @media | pas de flex/grid | pas de variables CSS | CSS tres court (434B) | aucun radius/ombre</t>
+          <t>layout en tableaux (6) | pas de @media | pas de variables CSS</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>lavillasaintmarc.com</t>
+          <t>egocentrik.fr</t>
         </is>
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>La Villa Saint-Marc</t>
+          <t>Egocentrik</t>
         </is>
       </c>
       <c r="C9" s="16" t="inlineStr">
         <is>
-          <t>Rouen</t>
-        </is>
-      </c>
-      <c r="D9" s="17" t="inlineStr"/>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="D9" s="17" t="inlineStr">
+        <is>
+          <t>Montrouge (92120)</t>
+        </is>
+      </c>
       <c r="E9" s="18" t="inlineStr">
         <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="F9" s="19" t="n">
-        <v>42</v>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="F9" s="26" t="n">
+        <v>29</v>
       </c>
       <c r="G9" s="18" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H9" s="20" t="inlineStr">
         <is>
@@ -1442,61 +1462,61 @@
       </c>
       <c r="J9" s="22" t="inlineStr">
         <is>
-          <t>webacappella 4.6.18 free (win)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K9" s="23" t="inlineStr">
         <is>
-          <t>doctype ancien | non responsive | document.write | pas de @media | pas de flex/grid</t>
+          <t>balises &lt;font&gt; (1) | non responsive | police vintage</t>
         </is>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>leloupcoworking.fr</t>
+          <t>fleur-d-oranger.com</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Le Loup</t>
+          <t>Fleur d'oranger</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr"/>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="F10" s="19" t="n">
-        <v>41</v>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="F10" s="26" t="n">
+        <v>28</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H10" s="10" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
-      <c r="I10" s="10" t="inlineStr">
-        <is>
-          <t>non</t>
+      <c r="I10" s="11" t="inlineStr">
+        <is>
+          <t>oui</t>
         </is>
       </c>
       <c r="J10" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ionos mywebsite</t>
         </is>
       </c>
       <c r="K10" s="13" t="inlineStr">
         <is>
-          <t>non responsive | pas de @media | px uniquement | pas de variables CSS | aucun radius/ombre</t>
+          <t>balises &lt;font&gt; (2) | non responsive | pas de variables CSS</t>
         </is>
       </c>
     </row>
@@ -1615,34 +1635,34 @@
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>bouilloncapitole.fr</t>
+          <t>cortonbeachcortonkayakcassis.com</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>Le Bouillon Capitole</t>
+          <t>Corton Beach</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Marseille</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr"/>
       <c r="E4" s="8" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F4" s="19" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="G4" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="H4" s="10" t="inlineStr">
-        <is>
-          <t>non</t>
+        <v>3</v>
+      </c>
+      <c r="H4" s="11" t="inlineStr">
+        <is>
+          <t>oui</t>
         </is>
       </c>
       <c r="I4" s="11" t="inlineStr">
@@ -1657,46 +1677,50 @@
       </c>
       <c r="K4" s="13" t="inlineStr">
         <is>
-          <t>&lt;center&gt; | non responsive | pas de @media | pas de flex/grid | pas de variables CSS</t>
+          <t>layout en tableaux (5) | balises &lt;font&gt; (18) | pas de @media | pas de flex/grid | pas de variables CSS | aucun radius/ombre</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="14" t="inlineStr">
         <is>
-          <t>surlepouce.libanais.free.fr</t>
+          <t>brasserie-lacbourget.fr</t>
         </is>
       </c>
       <c r="B5" s="15" t="inlineStr">
         <is>
-          <t>Sur le Pouce</t>
+          <t>Brasserie du Lac</t>
         </is>
       </c>
       <c r="C5" s="16" t="inlineStr">
         <is>
-          <t>Paris</t>
-        </is>
-      </c>
-      <c r="D5" s="17" t="inlineStr"/>
+          <t>Chambery</t>
+        </is>
+      </c>
+      <c r="D5" s="17" t="inlineStr">
+        <is>
+          <t>Le Bourget-du-Lac (73370)</t>
+        </is>
+      </c>
       <c r="E5" s="18" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>73</t>
         </is>
       </c>
       <c r="F5" s="19" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="G5" s="18" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H5" s="20" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
-      <c r="I5" s="20" t="inlineStr">
-        <is>
-          <t>non</t>
+      <c r="I5" s="21" t="inlineStr">
+        <is>
+          <t>oui</t>
         </is>
       </c>
       <c r="J5" s="22" t="inlineStr">
@@ -1706,37 +1730,37 @@
       </c>
       <c r="K5" s="23" t="inlineStr">
         <is>
-          <t>layout en tableaux (8) | bgcolor= | sans doctype | non responsive</t>
+          <t>non responsive | pas de @media | pas de flex/grid | pas de variables CSS | CSS tres court (434B) | aucun radius/ombre</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>gindalle.fr</t>
+          <t>capnell.com</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Gin Dalle</t>
+          <t>Cap Nell</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Rochefort</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr"/>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>17</t>
         </is>
       </c>
       <c r="F6" s="19" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H6" s="10" t="inlineStr">
         <is>
@@ -1755,19 +1779,19 @@
       </c>
       <c r="K6" s="13" t="inlineStr">
         <is>
-          <t>layout en tableaux (4) | bgcolor= | sans doctype | non responsive</t>
+          <t>doctype ancien | non responsive | images .gif | pas de @media | pas de flex/grid | pas de variables CSS</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>toulousefruitsdemer.fr</t>
+          <t>bouilloncapitole.fr</t>
         </is>
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>La Cabane</t>
+          <t>Le Bouillon Capitole</t>
         </is>
       </c>
       <c r="C7" s="16" t="inlineStr">
@@ -1775,70 +1799,70 @@
           <t>Toulouse</t>
         </is>
       </c>
-      <c r="D7" s="17" t="inlineStr"/>
+      <c r="D7" s="25" t="inlineStr"/>
       <c r="E7" s="18" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
       <c r="F7" s="19" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="G7" s="18" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H7" s="20" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
-      <c r="I7" s="20" t="inlineStr">
-        <is>
-          <t>non</t>
+      <c r="I7" s="21" t="inlineStr">
+        <is>
+          <t>oui</t>
         </is>
       </c>
       <c r="J7" s="22" t="inlineStr">
         <is>
-          <t>wordpress 3.7.41</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K7" s="23" t="inlineStr">
         <is>
-          <t>doctype ancien | non responsive | pas de @media | pas de flex/grid</t>
+          <t>&lt;center&gt; | non responsive | pas de @media | pas de flex/grid | pas de variables CSS</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>crocknpizz.fr</t>
+          <t>huguette-et-henri.fr</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>C'rock n'pizz</t>
+          <t>Huguette &amp; Henri</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr"/>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>75</t>
         </is>
       </c>
       <c r="F8" s="19" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="H8" s="10" t="inlineStr">
-        <is>
-          <t>non</t>
+        <v>3</v>
+      </c>
+      <c r="H8" s="11" t="inlineStr">
+        <is>
+          <t>oui</t>
         </is>
       </c>
       <c r="I8" s="11" t="inlineStr">
@@ -1848,55 +1872,51 @@
       </c>
       <c r="J8" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>lscms</t>
         </is>
       </c>
       <c r="K8" s="13" t="inlineStr">
         <is>
-          <t>layout en tableaux (95) | &lt;center&gt; | non responsive | &lt;br&gt; en masse</t>
+          <t>balises &lt;font&gt; (2) | pas de @media | pas de flex/grid | pas de variables CSS | CSS tres court (564B) | aucun radius/ombre</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>bistrobest.fr</t>
+          <t>gindalle.fr</t>
         </is>
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>Bistro Best</t>
+          <t>Gin Dalle</t>
         </is>
       </c>
       <c r="C9" s="16" t="inlineStr">
         <is>
-          <t>Paris</t>
-        </is>
-      </c>
-      <c r="D9" s="24" t="inlineStr">
-        <is>
-          <t>Marly (78160)</t>
-        </is>
-      </c>
+          <t>Toulouse</t>
+        </is>
+      </c>
+      <c r="D9" s="25" t="inlineStr"/>
       <c r="E9" s="18" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>31</t>
         </is>
       </c>
       <c r="F9" s="19" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G9" s="18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H9" s="20" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
-      <c r="I9" s="20" t="inlineStr">
-        <is>
-          <t>non</t>
+      <c r="I9" s="21" t="inlineStr">
+        <is>
+          <t>oui</t>
         </is>
       </c>
       <c r="J9" s="22" t="inlineStr">
@@ -1906,37 +1926,37 @@
       </c>
       <c r="K9" s="23" t="inlineStr">
         <is>
-          <t>non responsive | document.write | pas de @media | police vintage</t>
+          <t>layout en tableaux (4) | bgcolor= | sans doctype | non responsive</t>
         </is>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>by-s.fr</t>
+          <t>crocknpizz.fr</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Le By S'</t>
+          <t>C'rock n'pizz</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr"/>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>69</t>
         </is>
       </c>
       <c r="F10" s="19" t="n">
         <v>37</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H10" s="10" t="inlineStr">
         <is>
@@ -1955,7 +1975,7 @@
       </c>
       <c r="K10" s="13" t="inlineStr">
         <is>
-          <t>non responsive | pas de @media | pas de flex/grid | aucun radius/ombre</t>
+          <t>layout en tableaux (95) | &lt;center&gt; | non responsive | &lt;br&gt; en masse</t>
         </is>
       </c>
     </row>
@@ -2074,34 +2094,30 @@
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>toyotagarageclaudy.com</t>
+          <t>aden-44.fr</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>Garage Claudy</t>
+          <t>Aden</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Lyon</t>
-        </is>
-      </c>
-      <c r="D4" s="26" t="inlineStr">
-        <is>
-          <t>Villeurbanne (69100)</t>
-        </is>
-      </c>
+          <t>Nantes</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr"/>
       <c r="E4" s="8" t="inlineStr">
         <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="F4" s="9" t="n">
-        <v>66</v>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="F4" s="26" t="n">
+        <v>32</v>
       </c>
       <c r="G4" s="8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H4" s="10" t="inlineStr">
         <is>
@@ -2115,46 +2131,50 @@
       </c>
       <c r="J4" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>wp rocket 3.23.1</t>
         </is>
       </c>
       <c r="K4" s="13" t="inlineStr">
         <is>
-          <t>balises &lt;font&gt; (2) | bgcolor= | doctype ancien | non responsive | images .gif | document.write | pas de @media | pas de flex/grid | pas de variables CSS | aucun radius/ombre</t>
+          <t>non responsive | pas de @media | pas de variables CSS</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="14" t="inlineStr">
         <is>
-          <t>garage-massot-aussonne.fr</t>
+          <t>ma-carrosserie-essey.fr</t>
         </is>
       </c>
       <c r="B5" s="15" t="inlineStr">
         <is>
-          <t>Garage Massot</t>
+          <t>Ma carrosserie</t>
         </is>
       </c>
       <c r="C5" s="16" t="inlineStr">
         <is>
-          <t>Toulouse</t>
-        </is>
-      </c>
-      <c r="D5" s="17" t="inlineStr"/>
+          <t>Nancy</t>
+        </is>
+      </c>
+      <c r="D5" s="17" t="inlineStr">
+        <is>
+          <t>Essey-les-Nancy (54270)</t>
+        </is>
+      </c>
       <c r="E5" s="18" t="inlineStr">
         <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="F5" s="9" t="n">
-        <v>56</v>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="F5" s="26" t="n">
+        <v>22</v>
       </c>
       <c r="G5" s="18" t="n">
-        <v>6</v>
-      </c>
-      <c r="H5" s="20" t="inlineStr">
-        <is>
-          <t>non</t>
+        <v>2</v>
+      </c>
+      <c r="H5" s="21" t="inlineStr">
+        <is>
+          <t>oui</t>
         </is>
       </c>
       <c r="I5" s="21" t="inlineStr">
@@ -2164,95 +2184,99 @@
       </c>
       <c r="J5" s="22" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>drupal 9 (https://www.drupal.org)</t>
         </is>
       </c>
       <c r="K5" s="23" t="inlineStr">
         <is>
-          <t>balises &lt;font&gt; (4) | non responsive | pas de @media | pas de flex/grid | pas de variables CSS | CSS tres court (434B) | aucun radius/ombre</t>
+          <t>pas de @media | pas de flex/grid | pas de variables CSS</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>attelage-remorque-lyon.com</t>
+          <t>carrosserie-tomatis.fr</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Attelage et remorque de Lyon</t>
+          <t>Tomatis</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Marseille</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr"/>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="F6" s="19" t="n">
-        <v>44</v>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F6" s="26" t="n">
+        <v>22</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="H6" s="10" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="I6" s="10" t="inlineStr">
-        <is>
-          <t>non</t>
+        <v>2</v>
+      </c>
+      <c r="H6" s="11" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="I6" s="11" t="inlineStr">
+        <is>
+          <t>oui</t>
         </is>
       </c>
       <c r="J6" s="12" t="inlineStr">
         <is>
-          <t>spip 3.1.3 [23214] - sarka-spip 3.4.6 [99617]</t>
+          <t>drupal 9 (https://www.drupal.org)</t>
         </is>
       </c>
       <c r="K6" s="13" t="inlineStr">
         <is>
-          <t>non responsive | images .gif | document.write | pas de @media | pas de flex/grid | aucun radius/ombre</t>
+          <t>pas de @media | pas de flex/grid | pas de variables CSS</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>monsieur-embrayage-35.com</t>
+          <t>garage-datez.fr</t>
         </is>
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>Monsieur Embrayage</t>
+          <t>Garage Datez</t>
         </is>
       </c>
       <c r="C7" s="16" t="inlineStr">
         <is>
-          <t>Rennes</t>
-        </is>
-      </c>
-      <c r="D7" s="17" t="inlineStr"/>
+          <t>Nancy</t>
+        </is>
+      </c>
+      <c r="D7" s="17" t="inlineStr">
+        <is>
+          <t>Faulx (54760)</t>
+        </is>
+      </c>
       <c r="E7" s="18" t="inlineStr">
         <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="F7" s="19" t="n">
-        <v>41</v>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="F7" s="26" t="n">
+        <v>20</v>
       </c>
       <c r="G7" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="H7" s="20" t="inlineStr">
-        <is>
-          <t>non</t>
+      <c r="H7" s="21" t="inlineStr">
+        <is>
+          <t>oui</t>
         </is>
       </c>
       <c r="I7" s="21" t="inlineStr">
@@ -2262,39 +2286,43 @@
       </c>
       <c r="J7" s="22" t="inlineStr">
         <is>
-          <t>website builder 12.0.7</t>
+          <t>wordpress 5.2.26</t>
         </is>
       </c>
       <c r="K7" s="23" t="inlineStr">
         <is>
-          <t>doctype ancien | non responsive | pas de @media | pas de flex/grid | pas de variables CSS</t>
+          <t>layout en tableaux (11) | &lt;br&gt; en masse | pas de variables CSS</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>aden-44.fr</t>
+          <t>garage-aymarvigier.fr</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Aden</t>
+          <t>Garage Aymar-Vigier</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Nantes</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr"/>
+          <t>Clermont-Ferrand</t>
+        </is>
+      </c>
+      <c r="D8" s="24" t="inlineStr">
+        <is>
+          <t>Pont-du-Chateau (63430)</t>
+        </is>
+      </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="F8" s="25" t="n">
-        <v>32</v>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="F8" s="26" t="n">
+        <v>20</v>
       </c>
       <c r="G8" s="8" t="n">
         <v>3</v>
@@ -2311,110 +2339,118 @@
       </c>
       <c r="J8" s="12" t="inlineStr">
         <is>
-          <t>wp rocket 3.23.1</t>
+          <t>webacappellafusion 4.1.2 sp3 classic</t>
         </is>
       </c>
       <c r="K8" s="13" t="inlineStr">
         <is>
-          <t>non responsive | pas de @media | pas de variables CSS</t>
+          <t>sans doctype | non responsive</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>saone-auto.fr</t>
+          <t>etsdeloute.com</t>
         </is>
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>Garage Renault</t>
+          <t>ETS Deloute</t>
         </is>
       </c>
       <c r="C9" s="16" t="inlineStr">
         <is>
-          <t>Besancon</t>
-        </is>
-      </c>
-      <c r="D9" s="17" t="inlineStr"/>
+          <t>Aix-en-Provence</t>
+        </is>
+      </c>
+      <c r="D9" s="17" t="inlineStr">
+        <is>
+          <t>Velaux (13880)</t>
+        </is>
+      </c>
       <c r="E9" s="18" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="F9" s="25" t="n">
-        <v>29</v>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F9" s="26" t="n">
+        <v>20</v>
       </c>
       <c r="G9" s="18" t="n">
-        <v>8</v>
-      </c>
-      <c r="H9" s="20" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="I9" s="20" t="inlineStr">
-        <is>
-          <t>non</t>
+        <v>2</v>
+      </c>
+      <c r="H9" s="21" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="I9" s="21" t="inlineStr">
+        <is>
+          <t>oui</t>
         </is>
       </c>
       <c r="J9" s="22" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>masterslider 3.2.14 - responsive touch image slider</t>
         </is>
       </c>
       <c r="K9" s="23" t="inlineStr">
         <is>
-          <t>frameset | doctype ancien | non responsive</t>
+          <t>images .gif | pas de @media | pas de variables CSS</t>
         </is>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>berwald.fr</t>
+          <t>mecamoto17.com</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Neopart Fia Littoral</t>
+          <t>Meca Moto 17</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Nimes</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr"/>
+          <t>Rochefort</t>
+        </is>
+      </c>
+      <c r="D10" s="24" t="inlineStr">
+        <is>
+          <t>Tonnay-Charente (17430)</t>
+        </is>
+      </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="F10" s="25" t="n">
-        <v>25</v>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="F10" s="26" t="n">
+        <v>17</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="H10" s="10" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="I10" s="10" t="inlineStr">
-        <is>
-          <t>non</t>
+        <v>0</v>
+      </c>
+      <c r="H10" s="11" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="I10" s="11" t="inlineStr">
+        <is>
+          <t>oui</t>
         </is>
       </c>
       <c r="J10" s="12" t="inlineStr">
         <is>
-          <t>ort - ovh redirect technology</t>
+          <t>wix.com website builder</t>
         </is>
       </c>
       <c r="K10" s="13" t="inlineStr">
         <is>
-          <t>frameset | non responsive</t>
+          <t>pas de @media | pas de variables CSS</t>
         </is>
       </c>
     </row>
@@ -2533,34 +2569,34 @@
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>depuy.free.fr</t>
+          <t>clicadom.info</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>SAV Depuy</t>
+          <t>Clic@Dom</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Paris</t>
-        </is>
-      </c>
-      <c r="D4" s="26" t="inlineStr">
-        <is>
-          <t>Saint Brice sous Fort (95350)</t>
+          <t>Toulouse</t>
+        </is>
+      </c>
+      <c r="D4" s="24" t="inlineStr">
+        <is>
+          <t>Ramonville-Saint-Agne (31520)</t>
         </is>
       </c>
       <c r="E4" s="8" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>31</t>
         </is>
       </c>
       <c r="F4" s="19" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="G4" s="8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H4" s="10" t="inlineStr">
         <is>
@@ -2574,42 +2610,46 @@
       </c>
       <c r="J4" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>webacappella 4.6.13  professional (win) #45b8</t>
         </is>
       </c>
       <c r="K4" s="13" t="inlineStr">
         <is>
-          <t>balises &lt;font&gt; (57) | bgcolor= | sans doctype | non responsive | images .gif</t>
+          <t>doctype ancien | non responsive | document.write | pas de @media | pas de flex/grid</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="14" t="inlineStr">
         <is>
-          <t>cs2m.fr</t>
+          <t>barcavelos.fr</t>
         </is>
       </c>
       <c r="B5" s="15" t="inlineStr">
         <is>
-          <t>CS2M - Cordonnerie Serrurerie</t>
+          <t>Barca Vélo</t>
         </is>
       </c>
       <c r="C5" s="16" t="inlineStr">
         <is>
-          <t>Toulouse</t>
-        </is>
-      </c>
-      <c r="D5" s="17" t="inlineStr"/>
+          <t>Perpignan</t>
+        </is>
+      </c>
+      <c r="D5" s="17" t="inlineStr">
+        <is>
+          <t>Bompas (66430)</t>
+        </is>
+      </c>
       <c r="E5" s="18" t="inlineStr">
         <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="F5" s="25" t="n">
-        <v>34</v>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="F5" s="19" t="n">
+        <v>42</v>
       </c>
       <c r="G5" s="18" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H5" s="20" t="inlineStr">
         <is>
@@ -2628,86 +2668,90 @@
       </c>
       <c r="K5" s="23" t="inlineStr">
         <is>
-          <t>non responsive | pas de @media | pas de flex/grid</t>
+          <t>non responsive | document.write | pas de @media | pas de flex/grid | police vintage</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>pressingleluxembourg.com</t>
+          <t>ateliers-savary.com</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Le Luxembourg</t>
+          <t>Ateliers Savary</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr"/>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="F6" s="25" t="n">
-        <v>32</v>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="F6" s="19" t="n">
+        <v>42</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H6" s="10" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
-      <c r="I6" s="10" t="inlineStr">
-        <is>
-          <t>non</t>
+      <c r="I6" s="11" t="inlineStr">
+        <is>
+          <t>oui</t>
         </is>
       </c>
       <c r="J6" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>webacappella 4.6.27  personal (win) #5a37</t>
         </is>
       </c>
       <c r="K6" s="13" t="inlineStr">
         <is>
-          <t>non responsive | pas de @media | pas de variables CSS</t>
+          <t>doctype ancien | non responsive | document.write | pas de @media | pas de flex/grid</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>floriansbikes.com</t>
+          <t>pc-net.fr</t>
         </is>
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>Florian's Bikes</t>
+          <t>Le Comptoir de PC-NET</t>
         </is>
       </c>
       <c r="C7" s="16" t="inlineStr">
         <is>
-          <t>Toulouse</t>
-        </is>
-      </c>
-      <c r="D7" s="17" t="inlineStr"/>
+          <t>Saint-Etienne</t>
+        </is>
+      </c>
+      <c r="D7" s="17" t="inlineStr">
+        <is>
+          <t>Veauche (42340)</t>
+        </is>
+      </c>
       <c r="E7" s="18" t="inlineStr">
         <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="F7" s="25" t="n">
-        <v>32</v>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="F7" s="19" t="n">
+        <v>37</v>
       </c>
       <c r="G7" s="18" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H7" s="20" t="inlineStr">
         <is>
@@ -2726,41 +2770,41 @@
       </c>
       <c r="K7" s="23" t="inlineStr">
         <is>
-          <t>non responsive | pas de @media | pas de variables CSS</t>
+          <t>non responsive | pas de @media | pas de flex/grid | aucun radius/ombre</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>autourducycle.fr</t>
+          <t>lav29.fr</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Autour du Cycle</t>
+          <t>Lav'29</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Paris</t>
-        </is>
-      </c>
-      <c r="D8" s="26" t="inlineStr">
-        <is>
-          <t>La Varenne Saint Hilaire (94210)</t>
+          <t>Brest</t>
+        </is>
+      </c>
+      <c r="D8" s="24" t="inlineStr">
+        <is>
+          <t>Landerneau (29800)</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="F8" s="25" t="n">
-        <v>29</v>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="F8" s="19" t="n">
+        <v>37</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H8" s="10" t="inlineStr">
         <is>
@@ -2779,46 +2823,46 @@
       </c>
       <c r="K8" s="13" t="inlineStr">
         <is>
-          <t>balises &lt;font&gt; (11) | non responsive | police vintage</t>
+          <t>non responsive | pas de @media | pas de flex/grid | aucun radius/ombre</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>cycle-naturel.com</t>
+          <t>cs2m.fr</t>
         </is>
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>Cycle Naturel</t>
+          <t>CS2M - Cordonnerie Serrurerie</t>
         </is>
       </c>
       <c r="C9" s="16" t="inlineStr">
         <is>
-          <t>Paris</t>
-        </is>
-      </c>
-      <c r="D9" s="17" t="inlineStr"/>
+          <t>Toulouse</t>
+        </is>
+      </c>
+      <c r="D9" s="25" t="inlineStr"/>
       <c r="E9" s="18" t="inlineStr">
         <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="F9" s="25" t="n">
-        <v>25</v>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="F9" s="26" t="n">
+        <v>34</v>
       </c>
       <c r="G9" s="18" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H9" s="20" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
-      <c r="I9" s="20" t="inlineStr">
-        <is>
-          <t>non</t>
+      <c r="I9" s="21" t="inlineStr">
+        <is>
+          <t>oui</t>
         </is>
       </c>
       <c r="J9" s="22" t="inlineStr">
@@ -2828,19 +2872,19 @@
       </c>
       <c r="K9" s="23" t="inlineStr">
         <is>
-          <t>frameset | non responsive</t>
+          <t>non responsive | pas de @media | pas de flex/grid</t>
         </is>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>3dinfomac.com</t>
+          <t>autourducycle.fr</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>3D Informatique</t>
+          <t>Autour du Cycle</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
@@ -2848,14 +2892,18 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr"/>
+      <c r="D10" s="24" t="inlineStr">
+        <is>
+          <t>La Varenne Saint Hilaire (94210)</t>
+        </is>
+      </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
           <t>75</t>
         </is>
       </c>
-      <c r="F10" s="25" t="n">
-        <v>25</v>
+      <c r="F10" s="26" t="n">
+        <v>29</v>
       </c>
       <c r="G10" s="8" t="n">
         <v>6</v>
@@ -2877,7 +2925,7 @@
       </c>
       <c r="K10" s="13" t="inlineStr">
         <is>
-          <t>balises &lt;font&gt; (7) | non responsive</t>
+          <t>balises &lt;font&gt; (11) | non responsive | police vintage</t>
         </is>
       </c>
     </row>
